--- a/Cruce_Periodico_Cupos_vs_Amortizacion_J501456380.xlsx
+++ b/Cruce_Periodico_Cupos_vs_Amortizacion_J501456380.xlsx
@@ -221,13 +221,13 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <b/>
-      <color rgb="FFFFFF"/>
+      <color rgb="0F172A"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
       <b/>
-      <color rgb="0F172A"/>
+      <color rgb="FFFFFF"/>
     </font>
   </fonts>
   <fills count="30">
@@ -399,13 +399,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0F172A"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF0F172A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -802,6 +802,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="334155"/>
       </left>
       <right style="thin">
@@ -812,21 +827,6 @@
       </top>
       <bottom style="medium">
         <color rgb="0F172A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="E2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="E2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="E2E8F0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1289,7 +1289,7 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="str">
-        <v>LÍNEA DE CRÉDITO ROTATIVA BS. 600.000.000,00 • BENEFICIARIO: Elías Rafael Trías Abreu (C.I. V-2.997.829 / R.I.F. V-23997829-7)</v>
+        <v>LÍNEA DE CRÉDITO ROTATIVA BS. 600.000.000,00 • BENEFICIARIO: Manuel Alejandro Becerra Luis (C.I. V-24.224.176 / R.I.F. V-24224176-9)</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -3780,13 +3780,13 @@
       <c r="A4" s="6" t="str">
         <v>Item</v>
       </c>
-      <c r="B4" s="32" t="str">
+      <c r="B4" s="33" t="str">
         <v>Base Jurídica Aplicable</v>
       </c>
-      <c r="C4" s="32" t="str">
+      <c r="C4" s="33" t="str">
         <v>Dictamen Contable y Fiscal</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="33" t="str">
         <v>Efecto Legal y Probatorio</v>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       <c r="A6" s="24" t="str">
         <v>2</v>
       </c>
-      <c r="B6" s="33" t="str">
+      <c r="B6" s="32" t="str">
         <v>Art. 72 Ley de Impuesto sobre la Renta (LISLR)</v>
       </c>
       <c r="C6" s="13" t="str">
@@ -3836,7 +3836,7 @@
       <c r="A8" s="24" t="str">
         <v>4</v>
       </c>
-      <c r="B8" s="33" t="str">
+      <c r="B8" s="32" t="str">
         <v>Art. 16 Numeral 3 de la Ley del IVA</v>
       </c>
       <c r="C8" s="13" t="str">
@@ -3869,7 +3869,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J239"/>
+  <dimension ref="A1:J261"/>
   <cols>
     <col min="1" max="1" width="24.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="9" t="str">
-        <v>Registro de orden y control estatutario de apertura de Línea de Crédito Rotativa General por Bs. 600.000.000,00 concedida a Elías Rafael Trías Abreu según Contrato Notariado LC-ONI-2026-0001 y Acta de Asamblea. VEN-NIF PYME Sección 11.</v>
+        <v>Registro de orden y control estatutario de apertura de Línea de Crédito Rotativa General por Bs. 600.000.000,00 concedida a Manuel Alejandro Becerra Luis según Contrato Notariado LC-ONI-2026-0001 y Acta de Asamblea. VEN-NIF PYME Sección 11.</v>
       </c>
     </row>
     <row r="8">
@@ -4052,7 +4052,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G11" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H11" s="10">
         <v>2000000</v>
@@ -4148,7 +4148,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G15" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H15" s="10">
         <v>365000</v>
@@ -4244,7 +4244,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G19" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H19" s="10">
         <v>835000</v>
@@ -4340,7 +4340,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G23" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H23" s="10">
         <v>4050000</v>
@@ -4436,7 +4436,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G27" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H27" s="10">
         <v>36000000</v>
@@ -4532,7 +4532,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G31" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H31" s="10">
         <v>500000</v>
@@ -4628,7 +4628,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G35" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H35" s="10">
         <v>32500000</v>
@@ -4724,7 +4724,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G39" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H39" s="10">
         <v>15000000</v>
@@ -4820,7 +4820,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G43" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H43" s="10">
         <v>5000000</v>
@@ -4916,7 +4916,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G47" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H47" s="10">
         <v>5000000.01</v>
@@ -5012,7 +5012,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G51" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H51" s="10">
         <v>15000000</v>
@@ -5108,7 +5108,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G55" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H55" s="10">
         <v>10000000</v>
@@ -5204,7 +5204,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G59" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H59" s="10">
         <v>79790000</v>
@@ -5300,7 +5300,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G63" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H63" s="10">
         <v>5000000</v>
@@ -5396,7 +5396,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G67" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H67" s="10">
         <v>1000000</v>
@@ -5492,7 +5492,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G71" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H71" s="10">
         <v>565000</v>
@@ -5588,7 +5588,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G75" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H75" s="10">
         <v>26500000</v>
@@ -5684,7 +5684,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G79" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H79" s="10">
         <v>150000</v>
@@ -5780,7 +5780,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G83" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H83" s="10">
         <v>87900000</v>
@@ -5876,7 +5876,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G87" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H87" s="10">
         <v>13120000</v>
@@ -5972,7 +5972,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G91" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H91" s="10">
         <v>6875605.29</v>
@@ -6068,7 +6068,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G95" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H95" s="10">
         <v>102000</v>
@@ -6164,7 +6164,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G99" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H99" s="10">
         <v>101898000</v>
@@ -6260,7 +6260,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G103" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H103" s="10">
         <v>200000</v>
@@ -6356,7 +6356,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G107" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H107" s="10">
         <v>26400000</v>
@@ -6452,7 +6452,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G111" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H111" s="10">
         <v>825000</v>
@@ -6548,7 +6548,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G115" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H115" s="10">
         <v>825000</v>
@@ -6644,7 +6644,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G119" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H119" s="10">
         <v>1000000</v>
@@ -6740,7 +6740,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G123" s="9" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS</v>
       </c>
       <c r="H123" s="10">
         <v>20000000</v>
@@ -6836,16 +6836,16 @@
         <v>1.1.1.02.01</v>
       </c>
       <c r="G127" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
       </c>
       <c r="H127" s="10">
-        <v>1458707.38</v>
+        <v>1500000</v>
       </c>
       <c r="I127" s="10">
         <v>0</v>
       </c>
       <c r="J127" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 1.500.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 825.852,42) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 41.292,62) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 674.147,58). Saldo deudor resultante: Bs. Bs. 370.959.443,09. Soporte: Recibo RP-ONI-2026-0001 y Ref. Banesco TRFMB-3600133147.</v>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 1.500.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 825.852,42) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 674.147,58). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 41.292,62), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 370.959.443,09. Soporte: Recibo RP-ONI-2026-0001 y Ref. Banesco TRFMB-3600133147.</v>
       </c>
     </row>
     <row r="128">
@@ -6868,7 +6868,7 @@
         <v>1.1.3.05.02</v>
       </c>
       <c r="G128" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H128" s="14">
         <v>41292.62</v>
@@ -6897,16 +6897,16 @@
         <v/>
       </c>
       <c r="F129" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="G129" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
       </c>
       <c r="H129" s="10">
         <v>0</v>
       </c>
       <c r="I129" s="10">
-        <v>825852.42</v>
+        <v>41292.62</v>
       </c>
       <c r="J129" s="9" t="str">
         <v/>
@@ -6929,115 +6929,115 @@
         <v/>
       </c>
       <c r="F130" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G130" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H130" s="14">
+        <v>0</v>
+      </c>
+      <c r="I130" s="14">
+        <v>825852.42</v>
+      </c>
+      <c r="J130" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B131" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C131" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D131" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E131" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F131" s="23" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G130" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H130" s="14">
-        <v>0</v>
-      </c>
-      <c r="I130" s="14">
+      <c r="G131" s="9" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H131" s="10">
+        <v>0</v>
+      </c>
+      <c r="I131" s="10">
         <v>674147.58</v>
       </c>
-      <c r="J130" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B131" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C131" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D131" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E131" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F131" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G131" s="25" t="str">
+      <c r="J131" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B132" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C132" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D132" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E132" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F132" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G132" s="25" t="str">
         <v>TOTAL COMP-PAG-0001:</v>
       </c>
-      <c r="H131" s="26">
-        <v>1500000</v>
-      </c>
-      <c r="I131" s="26">
-        <v>1500000</v>
-      </c>
-      <c r="J131" s="27" t="str">
+      <c r="H132" s="26">
+        <v>1541292.62</v>
+      </c>
+      <c r="I132" s="26">
+        <v>1541292.62</v>
+      </c>
+      <c r="J132" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="23" t="str">
+    <row r="134">
+      <c r="A134" s="24" t="str">
         <v>COMP-PAG-0002</v>
       </c>
-      <c r="B133" s="8" t="str">
+      <c r="B134" s="12" t="str">
         <v>2026-05-15</v>
       </c>
-      <c r="C133" s="9" t="str">
+      <c r="C134" s="13" t="str">
         <v>Pago Recibido N° 2 (Amortización e ISLR)</v>
       </c>
-      <c r="D133" s="8" t="str">
+      <c r="D134" s="12" t="str">
         <v>RP-ONI-2026-0002</v>
       </c>
-      <c r="E133" s="8" t="str">
+      <c r="E134" s="12" t="str">
         <v>TRFMB-61353987017</v>
       </c>
-      <c r="F133" s="23" t="str">
+      <c r="F134" s="24" t="str">
         <v>1.1.1.02.01</v>
       </c>
-      <c r="G133" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H133" s="10">
-        <v>13622529.94</v>
-      </c>
-      <c r="I133" s="10">
-        <v>0</v>
-      </c>
-      <c r="J133" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 13.700.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.549.401,16) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 77.470,06) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 12.150.598,84). Saldo deudor resultante: Bs. Bs. 375.199.690,78. Soporte: Recibo RP-ONI-2026-0002 y Ref. Banesco TRFMB-61353987017.</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B134" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C134" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D134" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E134" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F134" s="24" t="str">
-        <v>1.1.3.05.02</v>
-      </c>
       <c r="G134" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
       </c>
       <c r="H134" s="14">
-        <v>77470.06</v>
+        <v>13700000</v>
       </c>
       <c r="I134" s="14">
         <v>0</v>
       </c>
       <c r="J134" s="13" t="str">
-        <v/>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 13.700.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.549.401,16) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 12.150.598,84). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 77.470,06), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 375.199.690,78. Soporte: Recibo RP-ONI-2026-0002 y Ref. Banesco TRFMB-61353987017.</v>
       </c>
     </row>
     <row r="135">
@@ -7057,16 +7057,16 @@
         <v/>
       </c>
       <c r="F135" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>1.1.3.05.02</v>
       </c>
       <c r="G135" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H135" s="10">
-        <v>0</v>
+        <v>77470.06</v>
       </c>
       <c r="I135" s="10">
-        <v>1549401.16</v>
+        <v>0</v>
       </c>
       <c r="J135" s="9" t="str">
         <v/>
@@ -7089,147 +7089,147 @@
         <v/>
       </c>
       <c r="F136" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G136" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H136" s="14">
+        <v>0</v>
+      </c>
+      <c r="I136" s="14">
+        <v>77470.06</v>
+      </c>
+      <c r="J136" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B137" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C137" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D137" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E137" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F137" s="23" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G137" s="9" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H137" s="10">
+        <v>0</v>
+      </c>
+      <c r="I137" s="10">
+        <v>1549401.16</v>
+      </c>
+      <c r="J137" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B138" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C138" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D138" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E138" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F138" s="24" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G136" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H136" s="14">
-        <v>0</v>
-      </c>
-      <c r="I136" s="14">
+      <c r="G138" s="13" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H138" s="14">
+        <v>0</v>
+      </c>
+      <c r="I138" s="14">
         <v>12150598.84</v>
       </c>
-      <c r="J136" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B137" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C137" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D137" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E137" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F137" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G137" s="25" t="str">
+      <c r="J138" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B139" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C139" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D139" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E139" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F139" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G139" s="25" t="str">
         <v>TOTAL COMP-PAG-0002:</v>
       </c>
-      <c r="H137" s="26">
-        <v>13700000</v>
-      </c>
-      <c r="I137" s="26">
-        <v>13700000</v>
-      </c>
-      <c r="J137" s="27" t="str">
+      <c r="H139" s="26">
+        <v>13777470.06</v>
+      </c>
+      <c r="I139" s="26">
+        <v>13777470.06</v>
+      </c>
+      <c r="J139" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="23" t="str">
+    <row r="141">
+      <c r="A141" s="23" t="str">
         <v>COMP-PAG-0003</v>
       </c>
-      <c r="B139" s="8" t="str">
+      <c r="B141" s="8" t="str">
         <v>2026-05-25</v>
       </c>
-      <c r="C139" s="9" t="str">
+      <c r="C141" s="9" t="str">
         <v>Pago Recibido N° 3 (Amortización e ISLR)</v>
       </c>
-      <c r="D139" s="8" t="str">
+      <c r="D141" s="8" t="str">
         <v>RP-ONI-2026-0003</v>
       </c>
-      <c r="E139" s="8" t="str">
+      <c r="E141" s="8" t="str">
         <v>TRFMB-61455660227</v>
       </c>
-      <c r="F139" s="23" t="str">
+      <c r="F141" s="23" t="str">
         <v>1.1.1.02.01</v>
       </c>
-      <c r="G139" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H139" s="10">
-        <v>2914142.87</v>
-      </c>
-      <c r="I139" s="10">
-        <v>0</v>
-      </c>
-      <c r="J139" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 3.000.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.717.142,54) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 85.857,13) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 1.282.857,46). Saldo deudor resultante: Bs. Bs. 385.074.213,77. Soporte: Recibo RP-ONI-2026-0003 y Ref. Banesco TRFMB-61455660227.</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B140" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C140" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D140" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E140" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F140" s="24" t="str">
-        <v>1.1.3.05.02</v>
-      </c>
-      <c r="G140" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H140" s="14">
-        <v>85857.13</v>
-      </c>
-      <c r="I140" s="14">
-        <v>0</v>
-      </c>
-      <c r="J140" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B141" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C141" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D141" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E141" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F141" s="23" t="str">
-        <v>4.2.1.01.01</v>
-      </c>
       <c r="G141" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
       </c>
       <c r="H141" s="10">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="I141" s="10">
-        <v>1717142.54</v>
+        <v>0</v>
       </c>
       <c r="J141" s="9" t="str">
-        <v/>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 3.000.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.717.142,54) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 1.282.857,46). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 85.857,13), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 385.074.213,77. Soporte: Recibo RP-ONI-2026-0003 y Ref. Banesco TRFMB-61455660227.</v>
       </c>
     </row>
     <row r="142">
@@ -7249,243 +7249,275 @@
         <v/>
       </c>
       <c r="F142" s="24" t="str">
+        <v>1.1.3.05.02</v>
+      </c>
+      <c r="G142" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H142" s="14">
+        <v>85857.13</v>
+      </c>
+      <c r="I142" s="14">
+        <v>0</v>
+      </c>
+      <c r="J142" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B143" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C143" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D143" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E143" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F143" s="23" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G143" s="9" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H143" s="10">
+        <v>0</v>
+      </c>
+      <c r="I143" s="10">
+        <v>85857.13</v>
+      </c>
+      <c r="J143" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B144" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C144" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D144" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E144" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F144" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G144" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H144" s="14">
+        <v>0</v>
+      </c>
+      <c r="I144" s="14">
+        <v>1717142.54</v>
+      </c>
+      <c r="J144" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B145" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C145" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D145" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E145" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F145" s="23" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G142" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H142" s="14">
-        <v>0</v>
-      </c>
-      <c r="I142" s="14">
+      <c r="G145" s="9" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H145" s="10">
+        <v>0</v>
+      </c>
+      <c r="I145" s="10">
         <v>1282857.46</v>
       </c>
-      <c r="J142" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B143" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C143" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D143" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E143" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F143" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G143" s="25" t="str">
+      <c r="J145" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B146" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C146" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D146" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E146" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F146" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G146" s="25" t="str">
         <v>TOTAL COMP-PAG-0003:</v>
       </c>
-      <c r="H143" s="26">
-        <v>3000000</v>
-      </c>
-      <c r="I143" s="26">
-        <v>3000000</v>
-      </c>
-      <c r="J143" s="27" t="str">
+      <c r="H146" s="26">
+        <v>3085857.13</v>
+      </c>
+      <c r="I146" s="26">
+        <v>3085857.13</v>
+      </c>
+      <c r="J146" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="23" t="str">
+    <row r="148">
+      <c r="A148" s="24" t="str">
         <v>COMP-PAG-0004</v>
       </c>
-      <c r="B145" s="8" t="str">
+      <c r="B148" s="12" t="str">
         <v>2026-06-09</v>
       </c>
-      <c r="C145" s="9" t="str">
+      <c r="C148" s="13" t="str">
         <v>Pago Recibido N° 4 (Amortización e ISLR)</v>
       </c>
-      <c r="D145" s="8" t="str">
+      <c r="D148" s="12" t="str">
         <v>RP-ONI-2026-0004</v>
       </c>
-      <c r="E145" s="8" t="str">
+      <c r="E148" s="12" t="str">
         <v>TRFMB-61605464794</v>
       </c>
-      <c r="F145" s="23" t="str">
+      <c r="F148" s="24" t="str">
         <v>1.1.1.02.01</v>
       </c>
-      <c r="G145" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H145" s="10">
-        <v>36110645.98</v>
-      </c>
-      <c r="I145" s="10">
-        <v>0</v>
-      </c>
-      <c r="J145" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 36.248.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 2.747.080,49) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 137.354,02) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 33.500.919,51). Saldo deudor resultante: Bs. Bs. 378.561.153,39. Soporte: Recibo RP-ONI-2026-0004 y Ref. Banesco TRFMB-61605464794.</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B146" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C146" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D146" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E146" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F146" s="24" t="str">
+      <c r="G148" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H148" s="14">
+        <v>36248000</v>
+      </c>
+      <c r="I148" s="14">
+        <v>0</v>
+      </c>
+      <c r="J148" s="13" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 36.248.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 2.747.080,49) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 33.500.919,51). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 137.354,02), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 378.561.153,39. Soporte: Recibo RP-ONI-2026-0004 y Ref. Banesco TRFMB-61605464794.</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B149" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C149" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D149" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E149" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F149" s="23" t="str">
         <v>1.1.3.05.02</v>
       </c>
-      <c r="G146" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H146" s="14">
+      <c r="G149" s="9" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H149" s="10">
         <v>137354.02</v>
       </c>
-      <c r="I146" s="14">
-        <v>0</v>
-      </c>
-      <c r="J146" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B147" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C147" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D147" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E147" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F147" s="23" t="str">
+      <c r="I149" s="10">
+        <v>0</v>
+      </c>
+      <c r="J149" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B150" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C150" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D150" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E150" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F150" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G150" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H150" s="14">
+        <v>0</v>
+      </c>
+      <c r="I150" s="14">
+        <v>137354.02</v>
+      </c>
+      <c r="J150" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B151" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C151" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D151" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E151" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F151" s="23" t="str">
         <v>4.2.1.01.01</v>
       </c>
-      <c r="G147" s="9" t="str">
+      <c r="G151" s="9" t="str">
         <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
       </c>
-      <c r="H147" s="10">
-        <v>0</v>
-      </c>
-      <c r="I147" s="10">
+      <c r="H151" s="10">
+        <v>0</v>
+      </c>
+      <c r="I151" s="10">
         <v>2747080.49</v>
       </c>
-      <c r="J147" s="9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B148" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C148" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D148" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E148" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F148" s="24" t="str">
-        <v>1.1.2.03.01</v>
-      </c>
-      <c r="G148" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H148" s="14">
-        <v>0</v>
-      </c>
-      <c r="I148" s="14">
-        <v>33500919.51</v>
-      </c>
-      <c r="J148" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B149" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C149" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D149" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E149" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F149" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G149" s="25" t="str">
-        <v>TOTAL COMP-PAG-0004:</v>
-      </c>
-      <c r="H149" s="26">
-        <v>36248000</v>
-      </c>
-      <c r="I149" s="26">
-        <v>36248000</v>
-      </c>
-      <c r="J149" s="27" t="str">
-        <v>CUADRADO</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="23" t="str">
-        <v>COMP-PAG-0005</v>
-      </c>
-      <c r="B151" s="8" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="C151" s="9" t="str">
-        <v>Pago Recibido N° 5 (Amortización e ISLR)</v>
-      </c>
-      <c r="D151" s="8" t="str">
-        <v>RP-ONI-2026-0005</v>
-      </c>
-      <c r="E151" s="8" t="str">
-        <v>TRFMB-61605548129</v>
-      </c>
-      <c r="F151" s="23" t="str">
-        <v>1.1.1.02.01</v>
-      </c>
-      <c r="G151" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H151" s="10">
-        <v>3700000</v>
-      </c>
-      <c r="I151" s="10">
-        <v>0</v>
-      </c>
       <c r="J151" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 3.700.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 0,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 3.700.000,00). Saldo deudor resultante: Bs. Bs. 374.861.153,39. Soporte: Recibo RP-ONI-2026-0005 y Ref. Banesco TRFMB-61605548129.</v>
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -7505,147 +7537,147 @@
         <v/>
       </c>
       <c r="F152" s="24" t="str">
+        <v>1.1.2.03.01</v>
+      </c>
+      <c r="G152" s="13" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H152" s="14">
+        <v>0</v>
+      </c>
+      <c r="I152" s="14">
+        <v>33500919.51</v>
+      </c>
+      <c r="J152" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B153" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C153" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D153" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E153" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F153" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G153" s="25" t="str">
+        <v>TOTAL COMP-PAG-0004:</v>
+      </c>
+      <c r="H153" s="26">
+        <v>36385354.02</v>
+      </c>
+      <c r="I153" s="26">
+        <v>36385354.02</v>
+      </c>
+      <c r="J153" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="23" t="str">
+        <v>COMP-PAG-0005</v>
+      </c>
+      <c r="B155" s="8" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="C155" s="9" t="str">
+        <v>Pago Recibido N° 5 (Amortización e ISLR)</v>
+      </c>
+      <c r="D155" s="8" t="str">
+        <v>RP-ONI-2026-0005</v>
+      </c>
+      <c r="E155" s="8" t="str">
+        <v>TRFMB-61605548129</v>
+      </c>
+      <c r="F155" s="23" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G155" s="9" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H155" s="10">
+        <v>3700000</v>
+      </c>
+      <c r="I155" s="10">
+        <v>0</v>
+      </c>
+      <c r="J155" s="9" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 3.700.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 3.700.000,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 0,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 374.861.153,39. Soporte: Recibo RP-ONI-2026-0005 y Ref. Banesco TRFMB-61605548129.</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B156" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C156" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D156" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E156" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F156" s="24" t="str">
         <v>1.1.3.05.02</v>
       </c>
-      <c r="G152" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H152" s="14">
-        <v>0</v>
-      </c>
-      <c r="I152" s="14">
-        <v>0</v>
-      </c>
-      <c r="J152" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B153" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C153" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D153" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E153" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F153" s="23" t="str">
-        <v>4.2.1.01.01</v>
-      </c>
-      <c r="G153" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
-      </c>
-      <c r="H153" s="10">
-        <v>0</v>
-      </c>
-      <c r="I153" s="10">
-        <v>0</v>
-      </c>
-      <c r="J153" s="9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B154" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C154" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D154" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E154" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F154" s="24" t="str">
-        <v>1.1.2.03.01</v>
-      </c>
-      <c r="G154" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H154" s="14">
-        <v>0</v>
-      </c>
-      <c r="I154" s="14">
-        <v>3700000</v>
-      </c>
-      <c r="J154" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B155" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C155" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D155" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E155" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F155" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G155" s="25" t="str">
-        <v>TOTAL COMP-PAG-0005:</v>
-      </c>
-      <c r="H155" s="26">
-        <v>3700000</v>
-      </c>
-      <c r="I155" s="26">
-        <v>3700000</v>
-      </c>
-      <c r="J155" s="27" t="str">
-        <v>CUADRADO</v>
+      <c r="G156" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H156" s="14">
+        <v>0</v>
+      </c>
+      <c r="I156" s="14">
+        <v>0</v>
+      </c>
+      <c r="J156" s="13" t="str">
+        <v/>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="23" t="str">
-        <v>COMP-PAG-0006</v>
+      <c r="A157" s="8" t="str">
+        <v/>
       </c>
       <c r="B157" s="8" t="str">
-        <v>2026-06-16</v>
+        <v/>
       </c>
       <c r="C157" s="9" t="str">
-        <v>Pago Recibido N° 6 (Amortización e ISLR)</v>
+        <v/>
       </c>
       <c r="D157" s="8" t="str">
-        <v>RP-ONI-2026-0006</v>
+        <v/>
       </c>
       <c r="E157" s="8" t="str">
-        <v>TRFMB-61679071434</v>
+        <v/>
       </c>
       <c r="F157" s="23" t="str">
-        <v>1.1.1.02.01</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="G157" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
       </c>
       <c r="H157" s="10">
-        <v>24939136.72</v>
+        <v>0</v>
       </c>
       <c r="I157" s="10">
         <v>0</v>
       </c>
       <c r="J157" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 25.000.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.217.265,69) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 60.863,28) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 23.782.734,31). Saldo deudor resultante: Bs. Bs. 367.481.235,90. Soporte: Recibo RP-ONI-2026-0006 y Ref. Banesco TRFMB-61679071434.</v>
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -7665,13 +7697,13 @@
         <v/>
       </c>
       <c r="F158" s="24" t="str">
-        <v>1.1.3.05.02</v>
+        <v>4.2.1.01.01</v>
       </c>
       <c r="G158" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
       </c>
       <c r="H158" s="14">
-        <v>60863.28</v>
+        <v>0</v>
       </c>
       <c r="I158" s="14">
         <v>0</v>
@@ -7697,115 +7729,115 @@
         <v/>
       </c>
       <c r="F159" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>1.1.2.03.01</v>
       </c>
       <c r="G159" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
       </c>
       <c r="H159" s="10">
         <v>0</v>
       </c>
       <c r="I159" s="10">
-        <v>1217265.69</v>
+        <v>3700000</v>
       </c>
       <c r="J159" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B160" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C160" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D160" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E160" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F160" s="24" t="str">
-        <v>1.1.2.03.01</v>
-      </c>
-      <c r="G160" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H160" s="14">
-        <v>0</v>
-      </c>
-      <c r="I160" s="14">
-        <v>23782734.31</v>
-      </c>
-      <c r="J160" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B161" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C161" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D161" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E161" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F161" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G161" s="25" t="str">
-        <v>TOTAL COMP-PAG-0006:</v>
-      </c>
-      <c r="H161" s="26">
+      <c r="A160" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B160" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C160" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D160" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E160" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F160" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G160" s="25" t="str">
+        <v>TOTAL COMP-PAG-0005:</v>
+      </c>
+      <c r="H160" s="26">
+        <v>3700000</v>
+      </c>
+      <c r="I160" s="26">
+        <v>3700000</v>
+      </c>
+      <c r="J160" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="24" t="str">
+        <v>COMP-PAG-0006</v>
+      </c>
+      <c r="B162" s="12" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="C162" s="13" t="str">
+        <v>Pago Recibido N° 6 (Amortización e ISLR)</v>
+      </c>
+      <c r="D162" s="12" t="str">
+        <v>RP-ONI-2026-0006</v>
+      </c>
+      <c r="E162" s="12" t="str">
+        <v>TRFMB-61679071434</v>
+      </c>
+      <c r="F162" s="24" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G162" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H162" s="14">
         <v>25000000</v>
       </c>
-      <c r="I161" s="26">
-        <v>25000000</v>
-      </c>
-      <c r="J161" s="27" t="str">
-        <v>CUADRADO</v>
+      <c r="I162" s="14">
+        <v>0</v>
+      </c>
+      <c r="J162" s="13" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 25.000.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.217.265,69) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 23.782.734,31). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 60.863,28), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 367.481.235,90. Soporte: Recibo RP-ONI-2026-0006 y Ref. Banesco TRFMB-61679071434.</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="23" t="str">
-        <v>COMP-PAG-0007</v>
+      <c r="A163" s="8" t="str">
+        <v/>
       </c>
       <c r="B163" s="8" t="str">
-        <v>2026-07-14</v>
+        <v/>
       </c>
       <c r="C163" s="9" t="str">
-        <v>Pago Recibido N° 7 (Amortización e ISLR)</v>
+        <v/>
       </c>
       <c r="D163" s="8" t="str">
-        <v>RP-ONI-2026-0007</v>
+        <v/>
       </c>
       <c r="E163" s="8" t="str">
-        <v>TRFMB-3611756071</v>
+        <v/>
       </c>
       <c r="F163" s="23" t="str">
-        <v>1.1.1.02.01</v>
+        <v>1.1.3.05.02</v>
       </c>
       <c r="G163" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H163" s="10">
-        <v>2375000</v>
+        <v>60863.28</v>
       </c>
       <c r="I163" s="10">
         <v>0</v>
       </c>
       <c r="J163" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 2.500.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 2.500.000,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 125.000,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 0,00). Saldo deudor resultante: Bs. Bs. 449.025.205,55. Soporte: Recibo RP-ONI-2026-0007 y Ref. Banesco TRFMB-3611756071.</v>
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -7825,16 +7857,16 @@
         <v/>
       </c>
       <c r="F164" s="24" t="str">
-        <v>1.1.3.05.02</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="G164" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
       </c>
       <c r="H164" s="14">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="I164" s="14">
-        <v>0</v>
+        <v>60863.28</v>
       </c>
       <c r="J164" s="13" t="str">
         <v/>
@@ -7866,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="I165" s="10">
-        <v>2500000</v>
+        <v>1217265.69</v>
       </c>
       <c r="J165" s="9" t="str">
         <v/>
@@ -7892,13 +7924,13 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G166" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
       </c>
       <c r="H166" s="14">
         <v>0</v>
       </c>
       <c r="I166" s="14">
-        <v>0</v>
+        <v>23782734.31</v>
       </c>
       <c r="J166" s="13" t="str">
         <v/>
@@ -7924,13 +7956,13 @@
         <v/>
       </c>
       <c r="G167" s="25" t="str">
-        <v>TOTAL COMP-PAG-0007:</v>
+        <v>TOTAL COMP-PAG-0006:</v>
       </c>
       <c r="H167" s="26">
-        <v>2500000</v>
+        <v>25060863.28</v>
       </c>
       <c r="I167" s="26">
-        <v>2500000</v>
+        <v>25060863.28</v>
       </c>
       <c r="J167" s="27" t="str">
         <v>CUADRADO</v>
@@ -7938,34 +7970,34 @@
     </row>
     <row r="169">
       <c r="A169" s="23" t="str">
-        <v>COMP-PAG-0008</v>
+        <v>COMP-PAG-0007</v>
       </c>
       <c r="B169" s="8" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-14</v>
       </c>
       <c r="C169" s="9" t="str">
-        <v>Pago Recibido N° 8 (Amortización e ISLR)</v>
+        <v>Pago Recibido N° 7 (Amortización e ISLR)</v>
       </c>
       <c r="D169" s="8" t="str">
-        <v>RP-ONI-2026-0008</v>
+        <v>RP-ONI-2026-0007</v>
       </c>
       <c r="E169" s="8" t="str">
-        <v>TRFMB-61961302310</v>
+        <v>TRFMB-3611756071</v>
       </c>
       <c r="F169" s="23" t="str">
         <v>1.1.1.02.01</v>
       </c>
       <c r="G169" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
       </c>
       <c r="H169" s="10">
-        <v>939997.54</v>
+        <v>2500000</v>
       </c>
       <c r="I169" s="10">
         <v>0</v>
       </c>
       <c r="J169" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 950.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 200.049,14) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 10.002,46) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 749.950,86). Saldo deudor resultante: Bs. Bs. 449.360.605,67. Soporte: Recibo RP-ONI-2026-0008 y Ref. Banesco TRFMB-61961302310.</v>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 2.500.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 2.500.000,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 0,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 125.000,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 449.025.205,55. Soporte: Recibo RP-ONI-2026-0007 y Ref. Banesco TRFMB-3611756071.</v>
       </c>
     </row>
     <row r="170">
@@ -7988,10 +8020,10 @@
         <v>1.1.3.05.02</v>
       </c>
       <c r="G170" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H170" s="14">
-        <v>10002.46</v>
+        <v>125000</v>
       </c>
       <c r="I170" s="14">
         <v>0</v>
@@ -8017,16 +8049,16 @@
         <v/>
       </c>
       <c r="F171" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="G171" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
       </c>
       <c r="H171" s="10">
         <v>0</v>
       </c>
       <c r="I171" s="10">
-        <v>200049.14</v>
+        <v>125000</v>
       </c>
       <c r="J171" s="9" t="str">
         <v/>
@@ -8049,115 +8081,115 @@
         <v/>
       </c>
       <c r="F172" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G172" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H172" s="14">
+        <v>0</v>
+      </c>
+      <c r="I172" s="14">
+        <v>2500000</v>
+      </c>
+      <c r="J172" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B173" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C173" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D173" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E173" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F173" s="23" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G172" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H172" s="14">
-        <v>0</v>
-      </c>
-      <c r="I172" s="14">
-        <v>749950.86</v>
-      </c>
-      <c r="J172" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B173" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C173" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D173" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E173" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F173" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G173" s="25" t="str">
-        <v>TOTAL COMP-PAG-0008:</v>
-      </c>
-      <c r="H173" s="26">
+      <c r="G173" s="9" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H173" s="10">
+        <v>0</v>
+      </c>
+      <c r="I173" s="10">
+        <v>0</v>
+      </c>
+      <c r="J173" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B174" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C174" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D174" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E174" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F174" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G174" s="25" t="str">
+        <v>TOTAL COMP-PAG-0007:</v>
+      </c>
+      <c r="H174" s="26">
+        <v>2625000</v>
+      </c>
+      <c r="I174" s="26">
+        <v>2625000</v>
+      </c>
+      <c r="J174" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="24" t="str">
+        <v>COMP-PAG-0008</v>
+      </c>
+      <c r="B176" s="12" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="C176" s="13" t="str">
+        <v>Pago Recibido N° 8 (Amortización e ISLR)</v>
+      </c>
+      <c r="D176" s="12" t="str">
+        <v>RP-ONI-2026-0008</v>
+      </c>
+      <c r="E176" s="12" t="str">
+        <v>TRFMB-61961302310</v>
+      </c>
+      <c r="F176" s="24" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G176" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H176" s="14">
         <v>950000</v>
       </c>
-      <c r="I173" s="26">
-        <v>950000</v>
-      </c>
-      <c r="J173" s="27" t="str">
-        <v>CUADRADO</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="23" t="str">
-        <v>COMP-PAG-0009</v>
-      </c>
-      <c r="B175" s="8" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="C175" s="9" t="str">
-        <v>Pago Recibido N° 9 (Amortización e ISLR)</v>
-      </c>
-      <c r="D175" s="8" t="str">
-        <v>RP-ONI-2026-0009</v>
-      </c>
-      <c r="E175" s="8" t="str">
-        <v>TRFMB-61991372259</v>
-      </c>
-      <c r="F175" s="23" t="str">
-        <v>1.1.1.02.01</v>
-      </c>
-      <c r="G175" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H175" s="10">
-        <v>190000</v>
-      </c>
-      <c r="I175" s="10">
-        <v>0</v>
-      </c>
-      <c r="J175" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 200.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 200.000,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 10.000,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 0,00). Saldo deudor resultante: Bs. Bs. 456.468.645,28. Soporte: Recibo RP-ONI-2026-0009 y Ref. Banesco TRFMB-61991372259.</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B176" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C176" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D176" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E176" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F176" s="24" t="str">
-        <v>1.1.3.05.02</v>
-      </c>
-      <c r="G176" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H176" s="14">
-        <v>10000</v>
-      </c>
       <c r="I176" s="14">
         <v>0</v>
       </c>
       <c r="J176" s="13" t="str">
-        <v/>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 950.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 200.049,14) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 749.950,86). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 10.002,46), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 449.360.605,67. Soporte: Recibo RP-ONI-2026-0008 y Ref. Banesco TRFMB-61961302310.</v>
       </c>
     </row>
     <row r="177">
@@ -8177,16 +8209,16 @@
         <v/>
       </c>
       <c r="F177" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>1.1.3.05.02</v>
       </c>
       <c r="G177" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H177" s="10">
-        <v>0</v>
+        <v>10002.46</v>
       </c>
       <c r="I177" s="10">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="J177" s="9" t="str">
         <v/>
@@ -8209,147 +8241,147 @@
         <v/>
       </c>
       <c r="F178" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G178" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H178" s="14">
+        <v>0</v>
+      </c>
+      <c r="I178" s="14">
+        <v>10002.46</v>
+      </c>
+      <c r="J178" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B179" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C179" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D179" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E179" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F179" s="23" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G179" s="9" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H179" s="10">
+        <v>0</v>
+      </c>
+      <c r="I179" s="10">
+        <v>200049.14</v>
+      </c>
+      <c r="J179" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B180" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C180" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D180" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E180" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F180" s="24" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G178" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H178" s="14">
-        <v>0</v>
-      </c>
-      <c r="I178" s="14">
-        <v>0</v>
-      </c>
-      <c r="J178" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B179" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C179" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D179" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E179" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F179" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G179" s="25" t="str">
-        <v>TOTAL COMP-PAG-0009:</v>
-      </c>
-      <c r="H179" s="26">
+      <c r="G180" s="13" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H180" s="14">
+        <v>0</v>
+      </c>
+      <c r="I180" s="14">
+        <v>749950.86</v>
+      </c>
+      <c r="J180" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B181" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C181" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D181" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E181" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F181" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G181" s="25" t="str">
+        <v>TOTAL COMP-PAG-0008:</v>
+      </c>
+      <c r="H181" s="26">
+        <v>960002.46</v>
+      </c>
+      <c r="I181" s="26">
+        <v>960002.46</v>
+      </c>
+      <c r="J181" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="23" t="str">
+        <v>COMP-PAG-0009</v>
+      </c>
+      <c r="B183" s="8" t="str">
+        <v>2026-07-20</v>
+      </c>
+      <c r="C183" s="9" t="str">
+        <v>Pago Recibido N° 9 (Amortización e ISLR)</v>
+      </c>
+      <c r="D183" s="8" t="str">
+        <v>RP-ONI-2026-0009</v>
+      </c>
+      <c r="E183" s="8" t="str">
+        <v>TRFMB-61991372259</v>
+      </c>
+      <c r="F183" s="23" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G183" s="9" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H183" s="10">
         <v>200000</v>
       </c>
-      <c r="I179" s="26">
-        <v>200000</v>
-      </c>
-      <c r="J179" s="27" t="str">
-        <v>CUADRADO</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="23" t="str">
-        <v>COMP-PAG-0010</v>
-      </c>
-      <c r="B181" s="8" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="C181" s="9" t="str">
-        <v>Pago Recibido N° 10 (Amortización e ISLR)</v>
-      </c>
-      <c r="D181" s="8" t="str">
-        <v>RP-ONI-2026-0010</v>
-      </c>
-      <c r="E181" s="8" t="str">
-        <v>TRFMB-62021317367</v>
-      </c>
-      <c r="F181" s="23" t="str">
-        <v>1.1.1.02.01</v>
-      </c>
-      <c r="G181" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H181" s="10">
-        <v>26389856.25</v>
-      </c>
-      <c r="I181" s="10">
-        <v>0</v>
-      </c>
-      <c r="J181" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 26.400.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 202.874,95) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 10.143,75) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 26.197.125,05). Saldo deudor resultante: Bs. Bs. 430.271.520,23. Soporte: Recibo RP-ONI-2026-0010 y Ref. Banesco TRFMB-62021317367.</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B182" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C182" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D182" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E182" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F182" s="24" t="str">
-        <v>1.1.3.05.02</v>
-      </c>
-      <c r="G182" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H182" s="14">
-        <v>10143.75</v>
-      </c>
-      <c r="I182" s="14">
-        <v>0</v>
-      </c>
-      <c r="J182" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B183" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C183" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D183" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E183" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F183" s="23" t="str">
-        <v>4.2.1.01.01</v>
-      </c>
-      <c r="G183" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
-      </c>
-      <c r="H183" s="10">
-        <v>0</v>
-      </c>
       <c r="I183" s="10">
-        <v>202874.95</v>
+        <v>0</v>
       </c>
       <c r="J183" s="9" t="str">
-        <v/>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 200.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 200.000,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 0,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 10.000,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 456.468.645,28. Soporte: Recibo RP-ONI-2026-0009 y Ref. Banesco TRFMB-61991372259.</v>
       </c>
     </row>
     <row r="184">
@@ -8369,243 +8401,275 @@
         <v/>
       </c>
       <c r="F184" s="24" t="str">
+        <v>1.1.3.05.02</v>
+      </c>
+      <c r="G184" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H184" s="14">
+        <v>10000</v>
+      </c>
+      <c r="I184" s="14">
+        <v>0</v>
+      </c>
+      <c r="J184" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B185" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C185" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D185" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E185" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F185" s="23" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G185" s="9" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H185" s="10">
+        <v>0</v>
+      </c>
+      <c r="I185" s="10">
+        <v>10000</v>
+      </c>
+      <c r="J185" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B186" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C186" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D186" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E186" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F186" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G186" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H186" s="14">
+        <v>0</v>
+      </c>
+      <c r="I186" s="14">
+        <v>200000</v>
+      </c>
+      <c r="J186" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B187" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C187" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D187" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E187" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F187" s="23" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G184" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H184" s="14">
-        <v>0</v>
-      </c>
-      <c r="I184" s="14">
-        <v>26197125.05</v>
-      </c>
-      <c r="J184" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B185" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C185" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D185" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E185" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F185" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G185" s="25" t="str">
-        <v>TOTAL COMP-PAG-0010:</v>
-      </c>
-      <c r="H185" s="26">
+      <c r="G187" s="9" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H187" s="10">
+        <v>0</v>
+      </c>
+      <c r="I187" s="10">
+        <v>0</v>
+      </c>
+      <c r="J187" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B188" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C188" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D188" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E188" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F188" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G188" s="25" t="str">
+        <v>TOTAL COMP-PAG-0009:</v>
+      </c>
+      <c r="H188" s="26">
+        <v>210000</v>
+      </c>
+      <c r="I188" s="26">
+        <v>210000</v>
+      </c>
+      <c r="J188" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="24" t="str">
+        <v>COMP-PAG-0010</v>
+      </c>
+      <c r="B190" s="12" t="str">
+        <v>2026-07-21</v>
+      </c>
+      <c r="C190" s="13" t="str">
+        <v>Pago Recibido N° 10 (Amortización e ISLR)</v>
+      </c>
+      <c r="D190" s="12" t="str">
+        <v>RP-ONI-2026-0010</v>
+      </c>
+      <c r="E190" s="12" t="str">
+        <v>TRFMB-62021317367</v>
+      </c>
+      <c r="F190" s="24" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G190" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H190" s="14">
         <v>26400000</v>
       </c>
-      <c r="I185" s="26">
-        <v>26400000</v>
-      </c>
-      <c r="J185" s="27" t="str">
-        <v>CUADRADO</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="23" t="str">
-        <v>COMP-PAG-0011</v>
-      </c>
-      <c r="B187" s="8" t="str">
-        <v>2026-07-27</v>
-      </c>
-      <c r="C187" s="9" t="str">
-        <v>Pago Recibido N° 11 (Amortización e ISLR)</v>
-      </c>
-      <c r="D187" s="8" t="str">
-        <v>RP-ONI-2026-0011</v>
-      </c>
-      <c r="E187" s="8" t="str">
-        <v>TRFMB-62089625117</v>
-      </c>
-      <c r="F187" s="23" t="str">
-        <v>1.1.1.02.01</v>
-      </c>
-      <c r="G187" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H187" s="10">
-        <v>11942241.38</v>
-      </c>
-      <c r="I187" s="10">
-        <v>0</v>
-      </c>
-      <c r="J187" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 12.000.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.155.172,49) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 57.758,62) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 10.844.827,51). Saldo deudor resultante: Bs. Bs. 422.344.856,12. Soporte: Recibo RP-ONI-2026-0011 y Ref. Banesco TRFMB-62089625117.</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B188" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C188" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D188" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E188" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F188" s="24" t="str">
+      <c r="I190" s="14">
+        <v>0</v>
+      </c>
+      <c r="J190" s="13" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 26.400.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 202.874,95) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 26.197.125,05). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 10.143,75), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 430.271.520,23. Soporte: Recibo RP-ONI-2026-0010 y Ref. Banesco TRFMB-62021317367.</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B191" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C191" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D191" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E191" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F191" s="23" t="str">
         <v>1.1.3.05.02</v>
       </c>
-      <c r="G188" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H188" s="14">
-        <v>57758.62</v>
-      </c>
-      <c r="I188" s="14">
-        <v>0</v>
-      </c>
-      <c r="J188" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B189" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C189" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D189" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E189" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F189" s="23" t="str">
+      <c r="G191" s="9" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H191" s="10">
+        <v>10143.75</v>
+      </c>
+      <c r="I191" s="10">
+        <v>0</v>
+      </c>
+      <c r="J191" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B192" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C192" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D192" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E192" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F192" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G192" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H192" s="14">
+        <v>0</v>
+      </c>
+      <c r="I192" s="14">
+        <v>10143.75</v>
+      </c>
+      <c r="J192" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B193" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C193" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D193" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E193" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F193" s="23" t="str">
         <v>4.2.1.01.01</v>
       </c>
-      <c r="G189" s="9" t="str">
+      <c r="G193" s="9" t="str">
         <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
       </c>
-      <c r="H189" s="10">
-        <v>0</v>
-      </c>
-      <c r="I189" s="10">
-        <v>1155172.49</v>
-      </c>
-      <c r="J189" s="9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B190" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C190" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D190" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E190" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F190" s="24" t="str">
-        <v>1.1.2.03.01</v>
-      </c>
-      <c r="G190" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H190" s="14">
-        <v>0</v>
-      </c>
-      <c r="I190" s="14">
-        <v>10844827.51</v>
-      </c>
-      <c r="J190" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B191" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C191" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D191" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E191" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F191" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G191" s="25" t="str">
-        <v>TOTAL COMP-PAG-0011:</v>
-      </c>
-      <c r="H191" s="26">
-        <v>12000000</v>
-      </c>
-      <c r="I191" s="26">
-        <v>12000000</v>
-      </c>
-      <c r="J191" s="27" t="str">
-        <v>CUADRADO</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="23" t="str">
-        <v>COMP-PAG-0012</v>
-      </c>
-      <c r="B193" s="8" t="str">
-        <v>2026-07-27</v>
-      </c>
-      <c r="C193" s="9" t="str">
-        <v>Pago Recibido N° 12 (Amortización e ISLR)</v>
-      </c>
-      <c r="D193" s="8" t="str">
-        <v>RP-ONI-2026-0012</v>
-      </c>
-      <c r="E193" s="8" t="str">
-        <v>TRFMB-62081509567</v>
-      </c>
-      <c r="F193" s="23" t="str">
-        <v>1.1.1.02.01</v>
-      </c>
-      <c r="G193" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
       <c r="H193" s="10">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="I193" s="10">
-        <v>0</v>
+        <v>202874.95</v>
       </c>
       <c r="J193" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 3.000.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 0,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 3.000.000,00). Saldo deudor resultante: Bs. Bs. 419.344.856,12. Soporte: Recibo RP-ONI-2026-0012 y Ref. Banesco TRFMB-62081509567.</v>
+        <v/>
       </c>
     </row>
     <row r="194">
@@ -8625,147 +8689,147 @@
         <v/>
       </c>
       <c r="F194" s="24" t="str">
+        <v>1.1.2.03.01</v>
+      </c>
+      <c r="G194" s="13" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H194" s="14">
+        <v>0</v>
+      </c>
+      <c r="I194" s="14">
+        <v>26197125.05</v>
+      </c>
+      <c r="J194" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B195" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C195" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D195" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E195" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F195" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G195" s="25" t="str">
+        <v>TOTAL COMP-PAG-0010:</v>
+      </c>
+      <c r="H195" s="26">
+        <v>26410143.75</v>
+      </c>
+      <c r="I195" s="26">
+        <v>26410143.75</v>
+      </c>
+      <c r="J195" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="23" t="str">
+        <v>COMP-PAG-0011</v>
+      </c>
+      <c r="B197" s="8" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C197" s="9" t="str">
+        <v>Pago Recibido N° 11 (Amortización e ISLR)</v>
+      </c>
+      <c r="D197" s="8" t="str">
+        <v>RP-ONI-2026-0011</v>
+      </c>
+      <c r="E197" s="8" t="str">
+        <v>TRFMB-62089625117</v>
+      </c>
+      <c r="F197" s="23" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G197" s="9" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H197" s="10">
+        <v>12000000</v>
+      </c>
+      <c r="I197" s="10">
+        <v>0</v>
+      </c>
+      <c r="J197" s="9" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 12.000.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.155.172,49) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 10.844.827,51). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 57.758,62), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 422.344.856,12. Soporte: Recibo RP-ONI-2026-0011 y Ref. Banesco TRFMB-62089625117.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B198" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C198" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D198" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E198" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F198" s="24" t="str">
         <v>1.1.3.05.02</v>
       </c>
-      <c r="G194" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H194" s="14">
-        <v>0</v>
-      </c>
-      <c r="I194" s="14">
-        <v>0</v>
-      </c>
-      <c r="J194" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B195" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C195" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D195" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E195" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F195" s="23" t="str">
-        <v>4.2.1.01.01</v>
-      </c>
-      <c r="G195" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
-      </c>
-      <c r="H195" s="10">
-        <v>0</v>
-      </c>
-      <c r="I195" s="10">
-        <v>0</v>
-      </c>
-      <c r="J195" s="9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B196" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C196" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D196" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E196" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F196" s="24" t="str">
-        <v>1.1.2.03.01</v>
-      </c>
-      <c r="G196" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H196" s="14">
-        <v>0</v>
-      </c>
-      <c r="I196" s="14">
-        <v>3000000</v>
-      </c>
-      <c r="J196" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B197" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C197" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D197" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E197" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F197" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G197" s="25" t="str">
-        <v>TOTAL COMP-PAG-0012:</v>
-      </c>
-      <c r="H197" s="26">
-        <v>3000000</v>
-      </c>
-      <c r="I197" s="26">
-        <v>3000000</v>
-      </c>
-      <c r="J197" s="27" t="str">
-        <v>CUADRADO</v>
+      <c r="G198" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H198" s="14">
+        <v>57758.62</v>
+      </c>
+      <c r="I198" s="14">
+        <v>0</v>
+      </c>
+      <c r="J198" s="13" t="str">
+        <v/>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="23" t="str">
-        <v>COMP-PAG-0013</v>
+      <c r="A199" s="8" t="str">
+        <v/>
       </c>
       <c r="B199" s="8" t="str">
-        <v>2026-07-27</v>
+        <v/>
       </c>
       <c r="C199" s="9" t="str">
-        <v>Pago Recibido N° 13 (Amortización e ISLR)</v>
+        <v/>
       </c>
       <c r="D199" s="8" t="str">
-        <v>RP-ONI-2026-0013</v>
+        <v/>
       </c>
       <c r="E199" s="8" t="str">
-        <v>TRFMB-62081531019</v>
+        <v/>
       </c>
       <c r="F199" s="23" t="str">
-        <v>1.1.1.02.01</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="G199" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
       </c>
       <c r="H199" s="10">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I199" s="10">
-        <v>0</v>
+        <v>57758.62</v>
       </c>
       <c r="J199" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 500.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 0,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 500.000,00). Saldo deudor resultante: Bs. Bs. 418.844.856,12. Soporte: Recibo RP-ONI-2026-0013 y Ref. Banesco TRFMB-62081531019.</v>
+        <v/>
       </c>
     </row>
     <row r="200">
@@ -8785,16 +8849,16 @@
         <v/>
       </c>
       <c r="F200" s="24" t="str">
-        <v>1.1.3.05.02</v>
+        <v>4.2.1.01.01</v>
       </c>
       <c r="G200" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
       </c>
       <c r="H200" s="14">
         <v>0</v>
       </c>
       <c r="I200" s="14">
-        <v>0</v>
+        <v>1155172.49</v>
       </c>
       <c r="J200" s="13" t="str">
         <v/>
@@ -8817,115 +8881,115 @@
         <v/>
       </c>
       <c r="F201" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>1.1.2.03.01</v>
       </c>
       <c r="G201" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
       </c>
       <c r="H201" s="10">
         <v>0</v>
       </c>
       <c r="I201" s="10">
-        <v>0</v>
+        <v>10844827.51</v>
       </c>
       <c r="J201" s="9" t="str">
         <v/>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B202" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C202" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D202" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E202" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F202" s="24" t="str">
-        <v>1.1.2.03.01</v>
-      </c>
-      <c r="G202" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H202" s="14">
-        <v>0</v>
-      </c>
-      <c r="I202" s="14">
-        <v>500000</v>
-      </c>
-      <c r="J202" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B203" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C203" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D203" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E203" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F203" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G203" s="25" t="str">
-        <v>TOTAL COMP-PAG-0013:</v>
-      </c>
-      <c r="H203" s="26">
-        <v>500000</v>
-      </c>
-      <c r="I203" s="26">
-        <v>500000</v>
-      </c>
-      <c r="J203" s="27" t="str">
+      <c r="A202" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B202" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C202" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D202" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E202" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F202" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G202" s="25" t="str">
+        <v>TOTAL COMP-PAG-0011:</v>
+      </c>
+      <c r="H202" s="26">
+        <v>12057758.62</v>
+      </c>
+      <c r="I202" s="26">
+        <v>12057758.62</v>
+      </c>
+      <c r="J202" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="24" t="str">
+        <v>COMP-PAG-0012</v>
+      </c>
+      <c r="B204" s="12" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C204" s="13" t="str">
+        <v>Pago Recibido N° 12 (Amortización e ISLR)</v>
+      </c>
+      <c r="D204" s="12" t="str">
+        <v>RP-ONI-2026-0012</v>
+      </c>
+      <c r="E204" s="12" t="str">
+        <v>TRFMB-62081509567</v>
+      </c>
+      <c r="F204" s="24" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G204" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H204" s="14">
+        <v>3000000</v>
+      </c>
+      <c r="I204" s="14">
+        <v>0</v>
+      </c>
+      <c r="J204" s="13" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 3.000.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 3.000.000,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 0,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 419.344.856,12. Soporte: Recibo RP-ONI-2026-0012 y Ref. Banesco TRFMB-62081509567.</v>
+      </c>
+    </row>
     <row r="205">
-      <c r="A205" s="23" t="str">
-        <v>COMP-PAG-0014</v>
+      <c r="A205" s="8" t="str">
+        <v/>
       </c>
       <c r="B205" s="8" t="str">
-        <v>2026-07-27</v>
+        <v/>
       </c>
       <c r="C205" s="9" t="str">
-        <v>Pago Recibido N° 14 (Amortización e ISLR)</v>
+        <v/>
       </c>
       <c r="D205" s="8" t="str">
-        <v>RP-ONI-2026-0014</v>
+        <v/>
       </c>
       <c r="E205" s="8" t="str">
-        <v>TRFMB-3613992496</v>
+        <v/>
       </c>
       <c r="F205" s="23" t="str">
-        <v>1.1.1.02.01</v>
+        <v>1.1.3.05.02</v>
       </c>
       <c r="G205" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H205" s="10">
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="I205" s="10">
         <v>0</v>
       </c>
       <c r="J205" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 330.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 0,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 330.000,00). Saldo deudor resultante: Bs. Bs. 418.514.856,12. Soporte: Recibo RP-ONI-2026-0014 y Ref. Banesco TRFMB-3613992496.</v>
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -8945,10 +9009,10 @@
         <v/>
       </c>
       <c r="F206" s="24" t="str">
-        <v>1.1.3.05.02</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="G206" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
       </c>
       <c r="H206" s="14">
         <v>0</v>
@@ -9012,13 +9076,13 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="G208" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
       </c>
       <c r="H208" s="14">
         <v>0</v>
       </c>
       <c r="I208" s="14">
-        <v>330000</v>
+        <v>3000000</v>
       </c>
       <c r="J208" s="13" t="str">
         <v/>
@@ -9044,13 +9108,13 @@
         <v/>
       </c>
       <c r="G209" s="25" t="str">
-        <v>TOTAL COMP-PAG-0014:</v>
+        <v>TOTAL COMP-PAG-0012:</v>
       </c>
       <c r="H209" s="26">
-        <v>330000</v>
+        <v>3000000</v>
       </c>
       <c r="I209" s="26">
-        <v>330000</v>
+        <v>3000000</v>
       </c>
       <c r="J209" s="27" t="str">
         <v>CUADRADO</v>
@@ -9058,34 +9122,34 @@
     </row>
     <row r="211">
       <c r="A211" s="23" t="str">
-        <v>COMP-PAG-0015</v>
+        <v>COMP-PAG-0013</v>
       </c>
       <c r="B211" s="8" t="str">
         <v>2026-07-27</v>
       </c>
       <c r="C211" s="9" t="str">
-        <v>Pago Recibido N° 15 (Amortización e ISLR)</v>
+        <v>Pago Recibido N° 13 (Amortización e ISLR)</v>
       </c>
       <c r="D211" s="8" t="str">
-        <v>RP-ONI-2026-0015</v>
+        <v>RP-ONI-2026-0013</v>
       </c>
       <c r="E211" s="8" t="str">
-        <v>TRFMB-3613993611</v>
+        <v>TRFMB-62081531019</v>
       </c>
       <c r="F211" s="23" t="str">
         <v>1.1.1.02.01</v>
       </c>
       <c r="G211" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
       </c>
       <c r="H211" s="10">
-        <v>248000</v>
+        <v>500000</v>
       </c>
       <c r="I211" s="10">
         <v>0</v>
       </c>
       <c r="J211" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 248.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 0,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 248.000,00). Saldo deudor resultante: Bs. Bs. 418.266.856,12. Soporte: Recibo RP-ONI-2026-0015 y Ref. Banesco TRFMB-3613993611.</v>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 500.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 500.000,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 0,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 418.844.856,12. Soporte: Recibo RP-ONI-2026-0013 y Ref. Banesco TRFMB-62081531019.</v>
       </c>
     </row>
     <row r="212">
@@ -9108,7 +9172,7 @@
         <v>1.1.3.05.02</v>
       </c>
       <c r="G212" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H212" s="14">
         <v>0</v>
@@ -9137,10 +9201,10 @@
         <v/>
       </c>
       <c r="F213" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="G213" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
       </c>
       <c r="H213" s="10">
         <v>0</v>
@@ -9169,115 +9233,115 @@
         <v/>
       </c>
       <c r="F214" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G214" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H214" s="14">
+        <v>0</v>
+      </c>
+      <c r="I214" s="14">
+        <v>0</v>
+      </c>
+      <c r="J214" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B215" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C215" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D215" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E215" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F215" s="23" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G214" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H214" s="14">
-        <v>0</v>
-      </c>
-      <c r="I214" s="14">
-        <v>248000</v>
-      </c>
-      <c r="J214" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B215" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C215" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D215" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E215" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F215" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G215" s="25" t="str">
-        <v>TOTAL COMP-PAG-0015:</v>
-      </c>
-      <c r="H215" s="26">
-        <v>248000</v>
-      </c>
-      <c r="I215" s="26">
-        <v>248000</v>
-      </c>
-      <c r="J215" s="27" t="str">
+      <c r="G215" s="9" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H215" s="10">
+        <v>0</v>
+      </c>
+      <c r="I215" s="10">
+        <v>500000</v>
+      </c>
+      <c r="J215" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B216" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C216" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D216" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E216" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F216" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G216" s="25" t="str">
+        <v>TOTAL COMP-PAG-0013:</v>
+      </c>
+      <c r="H216" s="26">
+        <v>500000</v>
+      </c>
+      <c r="I216" s="26">
+        <v>500000</v>
+      </c>
+      <c r="J216" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="23" t="str">
-        <v>COMP-PAG-0016</v>
-      </c>
-      <c r="B217" s="8" t="str">
-        <v>2026-07-29</v>
-      </c>
-      <c r="C217" s="9" t="str">
-        <v>Pago Recibido N° 16 (Amortización e ISLR)</v>
-      </c>
-      <c r="D217" s="8" t="str">
-        <v>RP-ONI-2026-0016</v>
-      </c>
-      <c r="E217" s="8" t="str">
-        <v>TRFMB-62106664904</v>
-      </c>
-      <c r="F217" s="23" t="str">
+    <row r="218">
+      <c r="A218" s="24" t="str">
+        <v>COMP-PAG-0014</v>
+      </c>
+      <c r="B218" s="12" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C218" s="13" t="str">
+        <v>Pago Recibido N° 14 (Amortización e ISLR)</v>
+      </c>
+      <c r="D218" s="12" t="str">
+        <v>RP-ONI-2026-0014</v>
+      </c>
+      <c r="E218" s="12" t="str">
+        <v>TRFMB-3613992496</v>
+      </c>
+      <c r="F218" s="24" t="str">
         <v>1.1.1.02.01</v>
       </c>
-      <c r="G217" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H217" s="10">
-        <v>21281360.27</v>
-      </c>
-      <c r="I217" s="10">
-        <v>0</v>
-      </c>
-      <c r="J217" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 21.300.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 372.794,59) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 18.639,73) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 20.927.205,41). Saldo deudor resultante: Bs. Bs. 398.466.705,28. Soporte: Recibo RP-ONI-2026-0016 y Ref. Banesco TRFMB-62106664904.</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B218" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C218" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D218" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E218" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F218" s="24" t="str">
-        <v>1.1.3.05.02</v>
-      </c>
       <c r="G218" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
       </c>
       <c r="H218" s="14">
-        <v>18639.73</v>
+        <v>330000</v>
       </c>
       <c r="I218" s="14">
         <v>0</v>
       </c>
       <c r="J218" s="13" t="str">
-        <v/>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 330.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 330.000,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 0,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 418.514.856,12. Soporte: Recibo RP-ONI-2026-0014 y Ref. Banesco TRFMB-3613992496.</v>
       </c>
     </row>
     <row r="219">
@@ -9297,16 +9361,16 @@
         <v/>
       </c>
       <c r="F219" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>1.1.3.05.02</v>
       </c>
       <c r="G219" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="H219" s="10">
         <v>0</v>
       </c>
       <c r="I219" s="10">
-        <v>372794.59</v>
+        <v>0</v>
       </c>
       <c r="J219" s="9" t="str">
         <v/>
@@ -9329,147 +9393,147 @@
         <v/>
       </c>
       <c r="F220" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G220" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H220" s="14">
+        <v>0</v>
+      </c>
+      <c r="I220" s="14">
+        <v>0</v>
+      </c>
+      <c r="J220" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B221" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C221" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D221" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E221" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F221" s="23" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G221" s="9" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H221" s="10">
+        <v>0</v>
+      </c>
+      <c r="I221" s="10">
+        <v>0</v>
+      </c>
+      <c r="J221" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B222" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C222" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D222" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E222" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F222" s="24" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G220" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H220" s="14">
-        <v>0</v>
-      </c>
-      <c r="I220" s="14">
-        <v>20927205.41</v>
-      </c>
-      <c r="J220" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B221" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C221" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D221" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E221" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F221" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G221" s="25" t="str">
-        <v>TOTAL COMP-PAG-0016:</v>
-      </c>
-      <c r="H221" s="26">
-        <v>21300000</v>
-      </c>
-      <c r="I221" s="26">
-        <v>21300000</v>
-      </c>
-      <c r="J221" s="27" t="str">
+      <c r="G222" s="13" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H222" s="14">
+        <v>0</v>
+      </c>
+      <c r="I222" s="14">
+        <v>330000</v>
+      </c>
+      <c r="J222" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B223" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C223" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D223" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E223" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F223" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G223" s="25" t="str">
+        <v>TOTAL COMP-PAG-0014:</v>
+      </c>
+      <c r="H223" s="26">
+        <v>330000</v>
+      </c>
+      <c r="I223" s="26">
+        <v>330000</v>
+      </c>
+      <c r="J223" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="23" t="str">
-        <v>COMP-PAG-0017</v>
-      </c>
-      <c r="B223" s="8" t="str">
-        <v>2026-07-29</v>
-      </c>
-      <c r="C223" s="9" t="str">
-        <v>Pago Recibido N° 17 (Amortización e ISLR)</v>
-      </c>
-      <c r="D223" s="8" t="str">
-        <v>RP-ONI-2026-0017</v>
-      </c>
-      <c r="E223" s="8" t="str">
-        <v>TRFMB-62106926077</v>
-      </c>
-      <c r="F223" s="23" t="str">
+    <row r="225">
+      <c r="A225" s="23" t="str">
+        <v>COMP-PAG-0015</v>
+      </c>
+      <c r="B225" s="8" t="str">
+        <v>2026-07-27</v>
+      </c>
+      <c r="C225" s="9" t="str">
+        <v>Pago Recibido N° 15 (Amortización e ISLR)</v>
+      </c>
+      <c r="D225" s="8" t="str">
+        <v>RP-ONI-2026-0015</v>
+      </c>
+      <c r="E225" s="8" t="str">
+        <v>TRFMB-3613993611</v>
+      </c>
+      <c r="F225" s="23" t="str">
         <v>1.1.1.02.01</v>
       </c>
-      <c r="G223" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H223" s="10">
-        <v>6800000</v>
-      </c>
-      <c r="I223" s="10">
-        <v>0</v>
-      </c>
-      <c r="J223" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 6.800.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 0,00) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 6.800.000,00). Saldo deudor resultante: Bs. Bs. 391.666.705,28. Soporte: Recibo RP-ONI-2026-0017 y Ref. Banesco TRFMB-62106926077.</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B224" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C224" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D224" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E224" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F224" s="24" t="str">
-        <v>1.1.3.05.02</v>
-      </c>
-      <c r="G224" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H224" s="14">
-        <v>0</v>
-      </c>
-      <c r="I224" s="14">
-        <v>0</v>
-      </c>
-      <c r="J224" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B225" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C225" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D225" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E225" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F225" s="23" t="str">
-        <v>4.2.1.01.01</v>
-      </c>
       <c r="G225" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
       </c>
       <c r="H225" s="10">
-        <v>0</v>
+        <v>248000</v>
       </c>
       <c r="I225" s="10">
         <v>0</v>
       </c>
       <c r="J225" s="9" t="str">
-        <v/>
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 248.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 248.000,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 0,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 418.266.856,12. Soporte: Recibo RP-ONI-2026-0015 y Ref. Banesco TRFMB-3613993611.</v>
       </c>
     </row>
     <row r="226">
@@ -9489,243 +9553,275 @@
         <v/>
       </c>
       <c r="F226" s="24" t="str">
+        <v>1.1.3.05.02</v>
+      </c>
+      <c r="G226" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H226" s="14">
+        <v>0</v>
+      </c>
+      <c r="I226" s="14">
+        <v>0</v>
+      </c>
+      <c r="J226" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B227" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C227" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D227" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E227" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F227" s="23" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G227" s="9" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H227" s="10">
+        <v>0</v>
+      </c>
+      <c r="I227" s="10">
+        <v>0</v>
+      </c>
+      <c r="J227" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B228" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C228" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D228" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E228" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F228" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G228" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H228" s="14">
+        <v>0</v>
+      </c>
+      <c r="I228" s="14">
+        <v>0</v>
+      </c>
+      <c r="J228" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B229" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C229" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D229" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E229" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F229" s="23" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="G226" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H226" s="14">
-        <v>0</v>
-      </c>
-      <c r="I226" s="14">
-        <v>6800000</v>
-      </c>
-      <c r="J226" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B227" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C227" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D227" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E227" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F227" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G227" s="25" t="str">
-        <v>TOTAL COMP-PAG-0017:</v>
-      </c>
-      <c r="H227" s="26">
-        <v>6800000</v>
-      </c>
-      <c r="I227" s="26">
-        <v>6800000</v>
-      </c>
-      <c r="J227" s="27" t="str">
+      <c r="G229" s="9" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H229" s="10">
+        <v>0</v>
+      </c>
+      <c r="I229" s="10">
+        <v>248000</v>
+      </c>
+      <c r="J229" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B230" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C230" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D230" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E230" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F230" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G230" s="25" t="str">
+        <v>TOTAL COMP-PAG-0015:</v>
+      </c>
+      <c r="H230" s="26">
+        <v>248000</v>
+      </c>
+      <c r="I230" s="26">
+        <v>248000</v>
+      </c>
+      <c r="J230" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="23" t="str">
-        <v>COMP-PAG-0018</v>
-      </c>
-      <c r="B229" s="8" t="str">
-        <v>2026-08-05</v>
-      </c>
-      <c r="C229" s="9" t="str">
-        <v>Pago Recibido N° 18 (Amortización e ISLR)</v>
-      </c>
-      <c r="D229" s="8" t="str">
-        <v>RP-ONI-2026-0018</v>
-      </c>
-      <c r="E229" s="8" t="str">
-        <v>TRFMB-62171461499</v>
-      </c>
-      <c r="F229" s="23" t="str">
+    <row r="232">
+      <c r="A232" s="24" t="str">
+        <v>COMP-PAG-0016</v>
+      </c>
+      <c r="B232" s="12" t="str">
+        <v>2026-07-29</v>
+      </c>
+      <c r="C232" s="13" t="str">
+        <v>Pago Recibido N° 16 (Amortización e ISLR)</v>
+      </c>
+      <c r="D232" s="12" t="str">
+        <v>RP-ONI-2026-0016</v>
+      </c>
+      <c r="E232" s="12" t="str">
+        <v>TRFMB-62106664904</v>
+      </c>
+      <c r="F232" s="24" t="str">
         <v>1.1.1.02.01</v>
       </c>
-      <c r="G229" s="9" t="str">
-        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Entrada Neta]</v>
-      </c>
-      <c r="H229" s="10">
-        <v>28938179.29</v>
-      </c>
-      <c r="I229" s="10">
-        <v>0</v>
-      </c>
-      <c r="J229" s="9" t="str">
-        <v>Cobranza de transferencia Banesco de abono por Bs. Bs. 29.000.000,00. Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.236.414,19) según mandato del Art. 529 del Código de Comercio, reconociendo el anticipo de ISLR retenido en fuente (5% por Bs. Bs. 61.820,71) según Decreto N° 1.808 y el remanente a amortización efectiva del capital (Bs. Bs. 27.763.585,81). Saldo deudor resultante: Bs. Bs. 369.655.262,07. Soporte: Recibo RP-ONI-2026-0018 y Ref. Banesco TRFMB-62171461499.</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B230" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C230" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D230" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E230" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F230" s="24" t="str">
+      <c r="G232" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H232" s="14">
+        <v>21300000</v>
+      </c>
+      <c r="I232" s="14">
+        <v>0</v>
+      </c>
+      <c r="J232" s="13" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 21.300.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 372.794,59) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 20.927.205,41). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 18.639,73), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 398.466.705,28. Soporte: Recibo RP-ONI-2026-0016 y Ref. Banesco TRFMB-62106664904.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B233" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C233" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D233" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E233" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F233" s="23" t="str">
         <v>1.1.3.05.02</v>
       </c>
-      <c r="G230" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
-      </c>
-      <c r="H230" s="14">
-        <v>61820.71</v>
-      </c>
-      <c r="I230" s="14">
-        <v>0</v>
-      </c>
-      <c r="J230" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="8" t="str">
-        <v/>
-      </c>
-      <c r="B231" s="8" t="str">
-        <v/>
-      </c>
-      <c r="C231" s="9" t="str">
-        <v/>
-      </c>
-      <c r="D231" s="8" t="str">
-        <v/>
-      </c>
-      <c r="E231" s="8" t="str">
-        <v/>
-      </c>
-      <c r="F231" s="23" t="str">
+      <c r="G233" s="9" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H233" s="10">
+        <v>18639.73</v>
+      </c>
+      <c r="I233" s="10">
+        <v>0</v>
+      </c>
+      <c r="J233" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B234" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C234" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D234" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E234" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F234" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G234" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H234" s="14">
+        <v>0</v>
+      </c>
+      <c r="I234" s="14">
+        <v>18639.73</v>
+      </c>
+      <c r="J234" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B235" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C235" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D235" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E235" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F235" s="23" t="str">
         <v>4.2.1.01.01</v>
       </c>
-      <c r="G231" s="9" t="str">
+      <c r="G235" s="9" t="str">
         <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
       </c>
-      <c r="H231" s="10">
-        <v>0</v>
-      </c>
-      <c r="I231" s="10">
-        <v>1236414.19</v>
-      </c>
-      <c r="J231" s="9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="12" t="str">
-        <v/>
-      </c>
-      <c r="B232" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C232" s="13" t="str">
-        <v/>
-      </c>
-      <c r="D232" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E232" s="12" t="str">
-        <v/>
-      </c>
-      <c r="F232" s="24" t="str">
-        <v>1.1.2.03.01</v>
-      </c>
-      <c r="G232" s="13" t="str">
-        <v>Cuentas por Cobrar Socios y Directores - ELÍAS RAFAEL TRÍAS ABREU [Amortización Capital]</v>
-      </c>
-      <c r="H232" s="14">
-        <v>0</v>
-      </c>
-      <c r="I232" s="14">
-        <v>27763585.81</v>
-      </c>
-      <c r="J232" s="13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="25" t="str">
-        <v/>
-      </c>
-      <c r="B233" s="25" t="str">
-        <v/>
-      </c>
-      <c r="C233" s="25" t="str">
-        <v/>
-      </c>
-      <c r="D233" s="25" t="str">
-        <v/>
-      </c>
-      <c r="E233" s="25" t="str">
-        <v/>
-      </c>
-      <c r="F233" s="25" t="str">
-        <v/>
-      </c>
-      <c r="G233" s="25" t="str">
-        <v>TOTAL COMP-PAG-0018:</v>
-      </c>
-      <c r="H233" s="26">
-        <v>29000000</v>
-      </c>
-      <c r="I233" s="26">
-        <v>29000000</v>
-      </c>
-      <c r="J233" s="27" t="str">
-        <v>CUADRADO</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="23" t="str">
-        <v>COMP-ISLR-2026-0001</v>
-      </c>
-      <c r="B235" s="8" t="str">
-        <v>31/12/2026</v>
-      </c>
-      <c r="C235" s="9" t="str">
-        <v>Compensación Fiscal de ISLR Retenido</v>
-      </c>
-      <c r="D235" s="8" t="str">
-        <v>ARC-SENIAT-2026</v>
-      </c>
-      <c r="E235" s="8" t="str">
-        <v>COMP-ARC-ACUMULADO</v>
-      </c>
-      <c r="F235" s="23" t="str">
-        <v>2.1.3.01.01</v>
-      </c>
-      <c r="G235" s="9" t="str">
-        <v>Impuesto Sobre la Renta (ISLR) por Pagar (Pasivo Corriente)</v>
-      </c>
       <c r="H235" s="10">
-        <v>696202.38</v>
+        <v>0</v>
       </c>
       <c r="I235" s="10">
-        <v>0</v>
+        <v>372794.59</v>
       </c>
       <c r="J235" s="9" t="str">
-        <v>Compensación fiscal de retenciones de ISLR acumuladas por Bs. Bs. 696.202,38 practicadas al 5% sobre la totalidad de los intereses de mutuo devengados en el período 2026, conforme al Art. 9 del Decreto N° 1.808. Soportado formalmente con los Comprobantes de Retención ARC emitidos por el mutuario pagador, deduciéndose directamente de la cuota tributaria en la Declaración Definitiva de Rentas ante el SENIAT.</v>
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -9745,16 +9841,16 @@
         <v/>
       </c>
       <c r="F236" s="24" t="str">
-        <v>1.1.3.05.02</v>
+        <v>1.1.2.03.01</v>
       </c>
       <c r="G236" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios (5% Decreto 1808)</v>
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
       </c>
       <c r="H236" s="14">
         <v>0</v>
       </c>
       <c r="I236" s="14">
-        <v>696202.38</v>
+        <v>20927205.41</v>
       </c>
       <c r="J236" s="13" t="str">
         <v/>
@@ -9780,53 +9876,629 @@
         <v/>
       </c>
       <c r="G237" s="25" t="str">
-        <v>TOTAL COMP-ISLR-2026-0001:</v>
+        <v>TOTAL COMP-PAG-0016:</v>
       </c>
       <c r="H237" s="26">
-        <v>696202.38</v>
+        <v>21318639.73</v>
       </c>
       <c r="I237" s="26">
-        <v>696202.38</v>
+        <v>21318639.73</v>
       </c>
       <c r="J237" s="27" t="str">
         <v>CUADRADO</v>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="28" t="str">
-        <v/>
-      </c>
-      <c r="B239" s="28" t="str">
-        <v/>
-      </c>
-      <c r="C239" s="28" t="str">
-        <v/>
-      </c>
-      <c r="D239" s="28" t="str">
-        <v/>
-      </c>
-      <c r="E239" s="28" t="str">
-        <v/>
-      </c>
-      <c r="F239" s="28" t="str">
-        <v/>
-      </c>
-      <c r="G239" s="28" t="str">
+      <c r="A239" s="23" t="str">
+        <v>COMP-PAG-0017</v>
+      </c>
+      <c r="B239" s="8" t="str">
+        <v>2026-07-29</v>
+      </c>
+      <c r="C239" s="9" t="str">
+        <v>Pago Recibido N° 17 (Amortización e ISLR)</v>
+      </c>
+      <c r="D239" s="8" t="str">
+        <v>RP-ONI-2026-0017</v>
+      </c>
+      <c r="E239" s="8" t="str">
+        <v>TRFMB-62106926077</v>
+      </c>
+      <c r="F239" s="23" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G239" s="9" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H239" s="10">
+        <v>6800000</v>
+      </c>
+      <c r="I239" s="10">
+        <v>0</v>
+      </c>
+      <c r="J239" s="9" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 6.800.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 0,00) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 6.800.000,00). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 0,00), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 391.666.705,28. Soporte: Recibo RP-ONI-2026-0017 y Ref. Banesco TRFMB-62106926077.</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B240" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C240" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D240" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E240" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F240" s="24" t="str">
+        <v>1.1.3.05.02</v>
+      </c>
+      <c r="G240" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H240" s="14">
+        <v>0</v>
+      </c>
+      <c r="I240" s="14">
+        <v>0</v>
+      </c>
+      <c r="J240" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B241" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C241" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D241" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E241" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F241" s="23" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G241" s="9" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H241" s="10">
+        <v>0</v>
+      </c>
+      <c r="I241" s="10">
+        <v>0</v>
+      </c>
+      <c r="J241" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B242" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C242" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D242" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E242" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F242" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G242" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H242" s="14">
+        <v>0</v>
+      </c>
+      <c r="I242" s="14">
+        <v>0</v>
+      </c>
+      <c r="J242" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B243" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C243" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D243" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E243" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F243" s="23" t="str">
+        <v>1.1.2.03.01</v>
+      </c>
+      <c r="G243" s="9" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H243" s="10">
+        <v>0</v>
+      </c>
+      <c r="I243" s="10">
+        <v>6800000</v>
+      </c>
+      <c r="J243" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B244" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C244" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D244" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E244" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F244" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G244" s="25" t="str">
+        <v>TOTAL COMP-PAG-0017:</v>
+      </c>
+      <c r="H244" s="26">
+        <v>6800000</v>
+      </c>
+      <c r="I244" s="26">
+        <v>6800000</v>
+      </c>
+      <c r="J244" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="24" t="str">
+        <v>COMP-PAG-0018</v>
+      </c>
+      <c r="B246" s="12" t="str">
+        <v>2026-08-05</v>
+      </c>
+      <c r="C246" s="13" t="str">
+        <v>Pago Recibido N° 18 (Amortización e ISLR)</v>
+      </c>
+      <c r="D246" s="12" t="str">
+        <v>RP-ONI-2026-0018</v>
+      </c>
+      <c r="E246" s="12" t="str">
+        <v>TRFMB-62171461499</v>
+      </c>
+      <c r="F246" s="24" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G246" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 0134-0987-5128) [Cobranza Íntegra Socio]</v>
+      </c>
+      <c r="H246" s="14">
+        <v>29000000</v>
+      </c>
+      <c r="I246" s="14">
+        <v>0</v>
+      </c>
+      <c r="J246" s="13" t="str">
+        <v>Cobranza de transferencia Banesco por Bs. Bs. 29.000.000,00 transferida íntegramente por el socio Manuel Becerra (Persona Natural). Se imputa con prelación legal imperativa primero a intereses devengados (Bs. Bs. 1.236.414,19) según mandato del Art. 529 del Código de Comercio, y el remanente a amortización de capital (Bs. Bs. 27.763.585,81). Agrícola ONI C.A., en su condición legal de persona jurídica y agente de retención corporativo ante el SENIAT (Art. 9 num. 1 del Decreto N° 1.808 y Art. 27 del COT), practica la retención del 5% de ISLR (Bs. Bs. 61.820,71), registrando el pasivo tributario por enterar al Fisco y reconociendo el crédito fiscal a favor de la empresa para su compensación anual en la Forma DPJ-26. Saldo deudor resultante: Bs. Bs. 369.655.262,07. Soporte: Recibo RP-ONI-2026-0018 y Ref. Banesco TRFMB-62171461499.</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B247" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C247" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D247" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E247" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F247" s="23" t="str">
+        <v>1.1.3.05.02</v>
+      </c>
+      <c r="G247" s="9" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808) [Crédito Fiscal ONI]</v>
+      </c>
+      <c r="H247" s="10">
+        <v>61820.71</v>
+      </c>
+      <c r="I247" s="10">
+        <v>0</v>
+      </c>
+      <c r="J247" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B248" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C248" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D248" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E248" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F248" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G248" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Fiscal Asumido por Agrícola ONI C.A.)</v>
+      </c>
+      <c r="H248" s="14">
+        <v>0</v>
+      </c>
+      <c r="I248" s="14">
+        <v>61820.71</v>
+      </c>
+      <c r="J248" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="str">
+        <v/>
+      </c>
+      <c r="B249" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C249" s="9" t="str">
+        <v/>
+      </c>
+      <c r="D249" s="8" t="str">
+        <v/>
+      </c>
+      <c r="E249" s="8" t="str">
+        <v/>
+      </c>
+      <c r="F249" s="23" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="G249" s="9" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento (Art. 529 C.Com)</v>
+      </c>
+      <c r="H249" s="10">
+        <v>0</v>
+      </c>
+      <c r="I249" s="10">
+        <v>1236414.19</v>
+      </c>
+      <c r="J249" s="9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B250" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C250" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D250" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E250" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F250" s="24" t="str">
+        <v>1.1.2.03.01</v>
+      </c>
+      <c r="G250" s="13" t="str">
+        <v>Cuentas por Cobrar Socios y Directores - MANUEL ALEJANDRO BECERRA LUIS [Amortización Capital]</v>
+      </c>
+      <c r="H250" s="14">
+        <v>0</v>
+      </c>
+      <c r="I250" s="14">
+        <v>27763585.81</v>
+      </c>
+      <c r="J250" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B251" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C251" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D251" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E251" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F251" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G251" s="25" t="str">
+        <v>TOTAL COMP-PAG-0018:</v>
+      </c>
+      <c r="H251" s="26">
+        <v>29061820.71</v>
+      </c>
+      <c r="I251" s="26">
+        <v>29061820.71</v>
+      </c>
+      <c r="J251" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="23" t="str">
+        <v>COMP-SENIAT-2026-0001</v>
+      </c>
+      <c r="B253" s="8" t="str">
+        <v>30/11/2026</v>
+      </c>
+      <c r="C253" s="9" t="str">
+        <v>Enteramiento y Pago de Retenciones al SENIAT (Agrícola ONI C.A.)</v>
+      </c>
+      <c r="D253" s="8" t="str">
+        <v>PLANILLA-SENIAT-ISLR</v>
+      </c>
+      <c r="E253" s="8" t="str">
+        <v>TRF-SENIAT-BANESCO-5128</v>
+      </c>
+      <c r="F253" s="23" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="G253" s="9" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Tributario Extinguido)</v>
+      </c>
+      <c r="H253" s="10">
+        <v>696202.38</v>
+      </c>
+      <c r="I253" s="10">
+        <v>0</v>
+      </c>
+      <c r="J253" s="9" t="str">
+        <v>Pago y enteramiento bancario realizado por Agrícola ONI C.A. como agente de retención corporativo ante la cuenta recaudadora del SENIAT por concepto de las retenciones del 5% de ISLR acumuladas sobre intereses devengados por Bs. Bs. 696.202,38, cancelados mediante transferencia bancaria desde la cuenta Banesco 5128 según planilla del portal fiscal del SENIAT. Art. 9 del Decreto N° 1.808 y Art. 27 del COT.</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B254" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C254" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D254" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E254" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F254" s="24" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="G254" s="13" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 5128) [Pago al SENIAT por Agrícola ONI C.A.]</v>
+      </c>
+      <c r="H254" s="14">
+        <v>0</v>
+      </c>
+      <c r="I254" s="14">
+        <v>696202.38</v>
+      </c>
+      <c r="J254" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B255" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C255" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D255" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E255" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F255" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G255" s="25" t="str">
+        <v>TOTAL COMP-SENIAT-2026-0001:</v>
+      </c>
+      <c r="H255" s="26">
+        <v>696202.38</v>
+      </c>
+      <c r="I255" s="26">
+        <v>696202.38</v>
+      </c>
+      <c r="J255" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="23" t="str">
+        <v>COMP-ISLR-2026-0001</v>
+      </c>
+      <c r="B257" s="8" t="str">
+        <v>31/12/2026</v>
+      </c>
+      <c r="C257" s="9" t="str">
+        <v>Compensación Anual de ISLR en Declaración Definitiva DPJ-26</v>
+      </c>
+      <c r="D257" s="8" t="str">
+        <v>DPJ-26-SENIAT-2026</v>
+      </c>
+      <c r="E257" s="8" t="str">
+        <v>CERT-RET-SENIAT-ACUM</v>
+      </c>
+      <c r="F257" s="23" t="str">
+        <v>2.1.3.01.01</v>
+      </c>
+      <c r="G257" s="9" t="str">
+        <v>Impuesto Sobre la Renta (ISLR) por Pagar (Pasivo Corriente DPJ-26)</v>
+      </c>
+      <c r="H257" s="10">
+        <v>696202.38</v>
+      </c>
+      <c r="I257" s="10">
+        <v>0</v>
+      </c>
+      <c r="J257" s="9" t="str">
+        <v>Compensación fiscal del crédito tributario por retenciones de ISLR acumuladas por Bs. Bs. 696.202,38 efectivamente enteradas por Agrícola ONI C.A. ante el SENIAT durante el ejercicio fiscal 2026, deduciéndose formalmente de la cuota tributaria en la Declaración Definitiva de Rentas (Forma DPJ-26) de la compañía conforme al Art. 9 del Decreto 1808.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="12" t="str">
+        <v/>
+      </c>
+      <c r="B258" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C258" s="13" t="str">
+        <v/>
+      </c>
+      <c r="D258" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E258" s="12" t="str">
+        <v/>
+      </c>
+      <c r="F258" s="24" t="str">
+        <v>1.1.3.05.02</v>
+      </c>
+      <c r="G258" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808)</v>
+      </c>
+      <c r="H258" s="14">
+        <v>0</v>
+      </c>
+      <c r="I258" s="14">
+        <v>696202.38</v>
+      </c>
+      <c r="J258" s="13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B259" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C259" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D259" s="25" t="str">
+        <v/>
+      </c>
+      <c r="E259" s="25" t="str">
+        <v/>
+      </c>
+      <c r="F259" s="25" t="str">
+        <v/>
+      </c>
+      <c r="G259" s="25" t="str">
+        <v>TOTAL COMP-ISLR-2026-0001:</v>
+      </c>
+      <c r="H259" s="26">
+        <v>696202.38</v>
+      </c>
+      <c r="I259" s="26">
+        <v>696202.38</v>
+      </c>
+      <c r="J259" s="27" t="str">
+        <v>CUADRADO</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="28" t="str">
+        <v/>
+      </c>
+      <c r="B261" s="28" t="str">
+        <v/>
+      </c>
+      <c r="C261" s="28" t="str">
+        <v/>
+      </c>
+      <c r="D261" s="28" t="str">
+        <v/>
+      </c>
+      <c r="E261" s="28" t="str">
+        <v/>
+      </c>
+      <c r="F261" s="28" t="str">
+        <v/>
+      </c>
+      <c r="G261" s="28" t="str">
         <v>TOTAL GENERAL LIBRO DIARIO (SUMAS IGUALES):</v>
       </c>
-      <c r="H239" s="18">
-        <v>1285472807.68</v>
-      </c>
-      <c r="I239" s="18">
-        <v>1285472807.68</v>
-      </c>
-      <c r="J239" s="17" t="str">
+      <c r="H261" s="18">
+        <v>1286865212.44</v>
+      </c>
+      <c r="I261" s="18">
+        <v>1286865212.44</v>
+      </c>
+      <c r="J261" s="17" t="str">
         <v>CUADRADO AL CÉNTIMO (49 ASIENTOS AUDITADOS)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J239"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J261"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9854,7 +10526,7 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="str">
-        <v>LÍNEA DE CRÉDITO BS. 600.000.000,00 • BENEFICIARIO: Elías Rafael Trías Abreu</v>
+        <v>LÍNEA DE CRÉDITO BS. 600.000.000,00 • BENEFICIARIO: Manuel Alejandro Becerra Luis</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -10870,11 +11542,11 @@
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" customWidth="1"/>
     <col min="6" max="6" width="26.83203125" customWidth="1"/>
     <col min="7" max="7" width="24.83203125" customWidth="1"/>
     <col min="8" max="8" width="24.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
     <col min="10" max="10" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10885,12 +11557,12 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="str">
-        <v>MUTUARIO PAGADOR: Elías Rafael Trías Abreu • RÉGIMEN RETENCIONES: DECRETO N° 1.808 (ART. 9)</v>
+        <v>MUTUARIO PAGADOR: Manuel Alejandro Becerra Luis (PERSONA NATURAL) • AGENTE DE RETENCIÓN: AGRÍCOLA ONI, C.A. (PERSONA JURÍDICA)</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="str">
-        <v>PRELACIÓN OBLIGATORIA ART. 529 C.COM: INTERESES PRIMERO, RETENCIÓN 5% ISLR Y AMORTIZACIÓN A CAPITAL</v>
+        <v>PRELACIÓN OBLIGATORIA ART. 529 C.COM: COBRANZA ÍNTEGRA EN BANCO, INTERESES PRIMERO Y RETENCIÓN 5% ENTERABLE AL SENIAT</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1"/>
@@ -10908,10 +11580,10 @@
         <v>Referencia Banesco</v>
       </c>
       <c r="E5" s="30" t="str">
-        <v>Banco Banesco Neto (VES)</v>
+        <v>Cobranza Banco Banesco (VES)</v>
       </c>
       <c r="F5" s="30" t="str">
-        <v>Anticipo ISLR Retenido 5% (VES)</v>
+        <v>Retención ISLR 5% por Enterar (VES)</v>
       </c>
       <c r="G5" s="30" t="str">
         <v>Ingresos Intereses (VES)</v>
@@ -10920,7 +11592,7 @@
         <v>Amortizado a Capital (VES)</v>
       </c>
       <c r="I5" s="30" t="str">
-        <v>Total Pagado (VES)</v>
+        <v>Total Cobrado en Banco (VES)</v>
       </c>
       <c r="J5" s="29" t="str">
         <v>Glosa y Prelación Art. 529 C.Com</v>
@@ -10940,7 +11612,7 @@
         <v>TRFMB-3600133147</v>
       </c>
       <c r="E6" s="10">
-        <v>1458707.38</v>
+        <v>1500000</v>
       </c>
       <c r="F6" s="10">
         <v>41292.62</v>
@@ -10955,7 +11627,7 @@
         <v>1500000</v>
       </c>
       <c r="J6" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 825.852,42) y capital (Bs. Bs. 674.147,58) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 825.852,42) y capital (Bs. Bs. 674.147,58) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="7">
@@ -10972,7 +11644,7 @@
         <v>TRFMB-61353987017</v>
       </c>
       <c r="E7" s="14">
-        <v>13622529.94</v>
+        <v>13700000</v>
       </c>
       <c r="F7" s="14">
         <v>77470.06</v>
@@ -10987,7 +11659,7 @@
         <v>13700000</v>
       </c>
       <c r="J7" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 1.549.401,16) y capital (Bs. Bs. 12.150.598,84) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 1.549.401,16) y capital (Bs. Bs. 12.150.598,84) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="8">
@@ -11004,7 +11676,7 @@
         <v>TRFMB-61455660227</v>
       </c>
       <c r="E8" s="10">
-        <v>2914142.87</v>
+        <v>3000000</v>
       </c>
       <c r="F8" s="10">
         <v>85857.13</v>
@@ -11019,7 +11691,7 @@
         <v>3000000</v>
       </c>
       <c r="J8" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 1.717.142,54) y capital (Bs. Bs. 1.282.857,46) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 1.717.142,54) y capital (Bs. Bs. 1.282.857,46) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="9">
@@ -11036,7 +11708,7 @@
         <v>TRFMB-61605464794</v>
       </c>
       <c r="E9" s="14">
-        <v>36110645.98</v>
+        <v>36248000</v>
       </c>
       <c r="F9" s="14">
         <v>137354.02</v>
@@ -11051,7 +11723,7 @@
         <v>36248000</v>
       </c>
       <c r="J9" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 2.747.080,49) y capital (Bs. Bs. 33.500.919,51) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 2.747.080,49) y capital (Bs. Bs. 33.500.919,51) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="10">
@@ -11083,7 +11755,7 @@
         <v>3700000</v>
       </c>
       <c r="J10" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 3.700.000,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 3.700.000,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="11">
@@ -11100,7 +11772,7 @@
         <v>TRFMB-61679071434</v>
       </c>
       <c r="E11" s="14">
-        <v>24939136.72</v>
+        <v>25000000</v>
       </c>
       <c r="F11" s="14">
         <v>60863.28</v>
@@ -11115,7 +11787,7 @@
         <v>25000000</v>
       </c>
       <c r="J11" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 1.217.265,69) y capital (Bs. Bs. 23.782.734,31) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 1.217.265,69) y capital (Bs. Bs. 23.782.734,31) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="12">
@@ -11132,7 +11804,7 @@
         <v>TRFMB-3611756071</v>
       </c>
       <c r="E12" s="10">
-        <v>2375000</v>
+        <v>2500000</v>
       </c>
       <c r="F12" s="10">
         <v>125000</v>
@@ -11147,7 +11819,7 @@
         <v>2500000</v>
       </c>
       <c r="J12" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 2.500.000,00) y capital (Bs. Bs. 0,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 2.500.000,00) y capital (Bs. Bs. 0,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="13">
@@ -11164,7 +11836,7 @@
         <v>TRFMB-61961302310</v>
       </c>
       <c r="E13" s="14">
-        <v>939997.54</v>
+        <v>950000</v>
       </c>
       <c r="F13" s="14">
         <v>10002.46</v>
@@ -11179,7 +11851,7 @@
         <v>950000</v>
       </c>
       <c r="J13" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 200.049,14) y capital (Bs. Bs. 749.950,86) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 200.049,14) y capital (Bs. Bs. 749.950,86) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="14">
@@ -11196,7 +11868,7 @@
         <v>TRFMB-61991372259</v>
       </c>
       <c r="E14" s="10">
-        <v>190000</v>
+        <v>200000</v>
       </c>
       <c r="F14" s="10">
         <v>10000</v>
@@ -11211,7 +11883,7 @@
         <v>200000</v>
       </c>
       <c r="J14" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 200.000,00) y capital (Bs. Bs. 0,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 200.000,00) y capital (Bs. Bs. 0,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="15">
@@ -11228,7 +11900,7 @@
         <v>TRFMB-62021317367</v>
       </c>
       <c r="E15" s="14">
-        <v>26389856.25</v>
+        <v>26400000</v>
       </c>
       <c r="F15" s="14">
         <v>10143.75</v>
@@ -11243,7 +11915,7 @@
         <v>26400000</v>
       </c>
       <c r="J15" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 202.874,95) y capital (Bs. Bs. 26.197.125,05) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 202.874,95) y capital (Bs. Bs. 26.197.125,05) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="16">
@@ -11260,7 +11932,7 @@
         <v>TRFMB-62089625117</v>
       </c>
       <c r="E16" s="10">
-        <v>11942241.38</v>
+        <v>12000000</v>
       </c>
       <c r="F16" s="10">
         <v>57758.62</v>
@@ -11275,7 +11947,7 @@
         <v>12000000</v>
       </c>
       <c r="J16" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 1.155.172,49) y capital (Bs. Bs. 10.844.827,51) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 1.155.172,49) y capital (Bs. Bs. 10.844.827,51) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="17">
@@ -11307,7 +11979,7 @@
         <v>3000000</v>
       </c>
       <c r="J17" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 3.000.000,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 3.000.000,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="18">
@@ -11339,7 +12011,7 @@
         <v>500000</v>
       </c>
       <c r="J18" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 500.000,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 500.000,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="19">
@@ -11371,7 +12043,7 @@
         <v>330000</v>
       </c>
       <c r="J19" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 330.000,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 330.000,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="20">
@@ -11403,7 +12075,7 @@
         <v>248000</v>
       </c>
       <c r="J20" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 248.000,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 248.000,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="21">
@@ -11420,7 +12092,7 @@
         <v>TRFMB-62106664904</v>
       </c>
       <c r="E21" s="14">
-        <v>21281360.27</v>
+        <v>21300000</v>
       </c>
       <c r="F21" s="14">
         <v>18639.73</v>
@@ -11435,7 +12107,7 @@
         <v>21300000</v>
       </c>
       <c r="J21" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 372.794,59) y capital (Bs. Bs. 20.927.205,41) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 372.794,59) y capital (Bs. Bs. 20.927.205,41) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="22">
@@ -11467,7 +12139,7 @@
         <v>6800000</v>
       </c>
       <c r="J22" s="9" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 6.800.000,00) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 0,00) y capital (Bs. Bs. 6.800.000,00) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="23">
@@ -11484,7 +12156,7 @@
         <v>TRFMB-62171461499</v>
       </c>
       <c r="E23" s="14">
-        <v>28938179.29</v>
+        <v>29000000</v>
       </c>
       <c r="F23" s="14">
         <v>61820.71</v>
@@ -11499,7 +12171,7 @@
         <v>29000000</v>
       </c>
       <c r="J23" s="13" t="str">
-        <v>Abono de mutuo imputado con prelación legal a intereses (Bs. Bs. 1.236.414,19) y capital (Bs. Bs. 27.763.585,81) con retención 5% ISLR.</v>
+        <v>Cobranza íntegra recibida del socio (Persona Natural) imputada primero a intereses (Bs. Bs. 1.236.414,19) y capital (Bs. Bs. 27.763.585,81) con retención 5% ISLR enterable por ONI C.A. al SENIAT.</v>
       </c>
     </row>
     <row r="24">
@@ -11516,7 +12188,7 @@
         <v>18 Transferencias Banesco</v>
       </c>
       <c r="E24" s="18">
-        <v>185679797.62</v>
+        <v>186376000</v>
       </c>
       <c r="F24" s="18">
         <v>696202.38</v>
@@ -11543,7 +12215,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -11562,12 +12234,12 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="str">
-        <v>RÉGIMEN: DECRETO N° 1.808 (G.O. N° 36.203) • ARTÍCULO 9, NUMERAL 8 (INTERESES DE MUTUO)</v>
+        <v>AGENTE DE RETENCIÓN: AGRÍCOLA ONI, C.A. (PERSONA JURÍDICA) • RÉGIMEN: DECRETO N° 1.808 (ART. 9)</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="str">
-        <v>CRÉDITO FISCAL COMPROBANTES ARC DEDUCIBLE DIRECTAMENTE EN LA DECLARACIÓN DEFINITIVA DE RENTAS</v>
+        <v>PAGADOR: MANUEL BECERRA (PERSONA NATURAL - NO ES AGENTE DE RETENCIÓN) • ENTERAMIENTO AL SENIAT POR AGRÍCOLA ONI C.A.</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1"/>
@@ -11591,10 +12263,10 @@
         <v>Retención ISLR 5% (VES)</v>
       </c>
       <c r="G5" s="21" t="str">
-        <v>Comprobante ARC Ref.</v>
+        <v>Planilla / Comprobante Ref.</v>
       </c>
       <c r="H5" s="21" t="str">
-        <v>Estado Tributario</v>
+        <v>Estado Tributario y Enteramiento</v>
       </c>
     </row>
     <row r="6">
@@ -11617,10 +12289,10 @@
         <v>41292.62</v>
       </c>
       <c r="G6" s="23" t="str">
-        <v>ARC-2026-0001</v>
+        <v>PLAN-SENIAT-2026-0001</v>
       </c>
       <c r="H6" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="7">
@@ -11643,10 +12315,10 @@
         <v>77470.06</v>
       </c>
       <c r="G7" s="24" t="str">
-        <v>ARC-2026-0002</v>
+        <v>PLAN-SENIAT-2026-0002</v>
       </c>
       <c r="H7" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="8">
@@ -11669,10 +12341,10 @@
         <v>85857.13</v>
       </c>
       <c r="G8" s="23" t="str">
-        <v>ARC-2026-0003</v>
+        <v>PLAN-SENIAT-2026-0003</v>
       </c>
       <c r="H8" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="9">
@@ -11695,10 +12367,10 @@
         <v>137354.02</v>
       </c>
       <c r="G9" s="24" t="str">
-        <v>ARC-2026-0004</v>
+        <v>PLAN-SENIAT-2026-0004</v>
       </c>
       <c r="H9" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="10">
@@ -11721,10 +12393,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="23" t="str">
-        <v>ARC-2026-0005</v>
+        <v>PLAN-SENIAT-2026-0005</v>
       </c>
       <c r="H10" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="11">
@@ -11747,10 +12419,10 @@
         <v>60863.28</v>
       </c>
       <c r="G11" s="24" t="str">
-        <v>ARC-2026-0006</v>
+        <v>PLAN-SENIAT-2026-0006</v>
       </c>
       <c r="H11" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="12">
@@ -11773,10 +12445,10 @@
         <v>125000</v>
       </c>
       <c r="G12" s="23" t="str">
-        <v>ARC-2026-0007</v>
+        <v>PLAN-SENIAT-2026-0007</v>
       </c>
       <c r="H12" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="13">
@@ -11799,10 +12471,10 @@
         <v>10002.46</v>
       </c>
       <c r="G13" s="24" t="str">
-        <v>ARC-2026-0008</v>
+        <v>PLAN-SENIAT-2026-0008</v>
       </c>
       <c r="H13" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="14">
@@ -11825,10 +12497,10 @@
         <v>10000</v>
       </c>
       <c r="G14" s="23" t="str">
-        <v>ARC-2026-0009</v>
+        <v>PLAN-SENIAT-2026-0009</v>
       </c>
       <c r="H14" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="15">
@@ -11851,10 +12523,10 @@
         <v>10143.75</v>
       </c>
       <c r="G15" s="24" t="str">
-        <v>ARC-2026-0010</v>
+        <v>PLAN-SENIAT-2026-0010</v>
       </c>
       <c r="H15" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="16">
@@ -11877,10 +12549,10 @@
         <v>57758.62</v>
       </c>
       <c r="G16" s="23" t="str">
-        <v>ARC-2026-0011</v>
+        <v>PLAN-SENIAT-2026-0011</v>
       </c>
       <c r="H16" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="17">
@@ -11903,10 +12575,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="24" t="str">
-        <v>ARC-2026-0012</v>
+        <v>PLAN-SENIAT-2026-0012</v>
       </c>
       <c r="H17" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="18">
@@ -11929,10 +12601,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="23" t="str">
-        <v>ARC-2026-0013</v>
+        <v>PLAN-SENIAT-2026-0013</v>
       </c>
       <c r="H18" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="19">
@@ -11955,10 +12627,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="24" t="str">
-        <v>ARC-2026-0014</v>
+        <v>PLAN-SENIAT-2026-0014</v>
       </c>
       <c r="H19" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="20">
@@ -11981,10 +12653,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="23" t="str">
-        <v>ARC-2026-0015</v>
+        <v>PLAN-SENIAT-2026-0015</v>
       </c>
       <c r="H20" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="21">
@@ -12007,10 +12679,10 @@
         <v>18639.73</v>
       </c>
       <c r="G21" s="24" t="str">
-        <v>ARC-2026-0016</v>
+        <v>PLAN-SENIAT-2026-0016</v>
       </c>
       <c r="H21" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="22">
@@ -12033,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="G22" s="23" t="str">
-        <v>ARC-2026-0017</v>
+        <v>PLAN-SENIAT-2026-0017</v>
       </c>
       <c r="H22" s="9" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="23">
@@ -12059,10 +12731,10 @@
         <v>61820.71</v>
       </c>
       <c r="G23" s="24" t="str">
-        <v>ARC-2026-0018</v>
+        <v>PLAN-SENIAT-2026-0018</v>
       </c>
       <c r="H23" s="13" t="str">
-        <v>Crédito Fiscal Retenido en Fuente</v>
+        <v>Retenido y Enterado al SENIAT por ONI C.A.</v>
       </c>
     </row>
     <row r="24">
@@ -12085,15 +12757,15 @@
         <v>696202.38</v>
       </c>
       <c r="G24" s="16" t="str">
-        <v>18 Comprobantes ARC</v>
+        <v>18 Enteramientos SENIAT</v>
       </c>
       <c r="H24" s="17" t="str">
-        <v>Compensado contra ISLR Anual</v>
+        <v>Pagado al SENIAT y Compensado en DPJ-26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="str">
-        <v>ASIENTO DE CIERRE CONTABLE Y COMPENSACIÓN FISCAL:</v>
+        <v>ASIENTOS DE ENTERAMIENTO AL SENIAT Y COMPENSACIÓN FISCAL:</v>
       </c>
     </row>
     <row r="27">
@@ -12118,16 +12790,16 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="str">
-        <v>31/12/2026</v>
+        <v>30/11/2026</v>
       </c>
       <c r="B28" s="23" t="str">
-        <v>COMP-ISLR-2026-0001</v>
+        <v>COMP-SENIAT-2026-0001</v>
       </c>
       <c r="C28" s="23" t="str">
-        <v>2.1.3.01.01</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="D28" s="9" t="str">
-        <v>Impuesto Sobre la Renta (ISLR) por Pagar</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Extinguido)</v>
       </c>
       <c r="E28" s="10">
         <v>696202.38</v>
@@ -12138,16 +12810,16 @@
     </row>
     <row r="29">
       <c r="A29" s="12" t="str">
-        <v>31/12/2026</v>
+        <v>30/11/2026</v>
       </c>
       <c r="B29" s="24" t="str">
-        <v>COMP-ISLR-2026-0001</v>
+        <v>COMP-SENIAT-2026-0001</v>
       </c>
       <c r="C29" s="24" t="str">
-        <v>1.1.3.05.02</v>
+        <v>1.1.1.02.01</v>
       </c>
       <c r="D29" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes y Socios</v>
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 5128) [Pago al SENIAT por ONI C.A.]</v>
       </c>
       <c r="E29" s="14">
         <v>0</v>
@@ -12157,35 +12829,95 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="str">
-        <v/>
-      </c>
-      <c r="B30" s="28" t="str">
-        <v/>
-      </c>
-      <c r="C30" s="28" t="str">
-        <v/>
-      </c>
-      <c r="D30" s="28" t="str">
+      <c r="A30" s="25" t="str">
+        <v/>
+      </c>
+      <c r="B30" s="25" t="str">
+        <v/>
+      </c>
+      <c r="C30" s="25" t="str">
+        <v/>
+      </c>
+      <c r="D30" s="25" t="str">
+        <v>TOTAL ENTERAMIENTO AL SENIAT:</v>
+      </c>
+      <c r="E30" s="26">
+        <v>696202.38</v>
+      </c>
+      <c r="F30" s="26">
+        <v>696202.38</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="str">
+        <v>31/12/2026</v>
+      </c>
+      <c r="B31" s="23" t="str">
+        <v>COMP-ISLR-2026-0001</v>
+      </c>
+      <c r="C31" s="23" t="str">
+        <v>2.1.3.01.01</v>
+      </c>
+      <c r="D31" s="9" t="str">
+        <v>Impuesto Sobre la Renta (ISLR) por Pagar (Pasivo Corriente DPJ-26)</v>
+      </c>
+      <c r="E31" s="10">
+        <v>696202.38</v>
+      </c>
+      <c r="F31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="str">
+        <v>31/12/2026</v>
+      </c>
+      <c r="B32" s="24" t="str">
+        <v>COMP-ISLR-2026-0001</v>
+      </c>
+      <c r="C32" s="24" t="str">
+        <v>1.1.3.05.02</v>
+      </c>
+      <c r="D32" s="13" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Retención en Fuente - Dto. 1808)</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>696202.38</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="str">
+        <v/>
+      </c>
+      <c r="B33" s="28" t="str">
+        <v/>
+      </c>
+      <c r="C33" s="28" t="str">
+        <v/>
+      </c>
+      <c r="D33" s="28" t="str">
         <v>TOTAL ASIENTO DE COMPENSACIÓN:</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E33" s="18">
         <v>696202.38</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F33" s="18">
         <v>696202.38</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H33"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -12300,7 +13032,7 @@
         <v>1.1.2.03.01</v>
       </c>
       <c r="E7" s="9" t="str">
-        <v>Cuentas por Cobrar Socios - Elías Rafael Trías Abreu</v>
+        <v>Cuentas por Cobrar Socios - Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F7" s="10">
         <v>498400605.3</v>
@@ -12352,16 +13084,16 @@
         <v>1.1.1.02.01</v>
       </c>
       <c r="E9" s="9" t="str">
-        <v>Banco Banesco C.A. (Entrada Neta Líquida)</v>
+        <v>Banco Banesco C.A. (Cobranza Íntegra Socio)</v>
       </c>
       <c r="F9" s="10">
-        <v>185679797.62</v>
+        <v>186376000</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="str">
-        <v>Partida Cuádruple Art. 529 C.Com</v>
+        <v>Cobranza íntegra persona natural</v>
       </c>
     </row>
     <row r="10">
@@ -12378,7 +13110,7 @@
         <v>1.1.3.05.02</v>
       </c>
       <c r="E10" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes (5%)</v>
+        <v>Anticipo de ISLR por Compensar (5% Dto. 1808) [Crédito Fiscal ONI]</v>
       </c>
       <c r="F10" s="14">
         <v>696202.38</v>
@@ -12387,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="13" t="str">
-        <v>Decreto N° 1.808 Art. 9 Numeral 8</v>
+        <v>Crédito Fiscal Deducible DPJ-26</v>
       </c>
     </row>
     <row r="11">
@@ -12401,19 +13133,19 @@
         <v/>
       </c>
       <c r="D11" s="23" t="str">
-        <v>4.2.1.01.01</v>
+        <v>2.1.3.01.03</v>
       </c>
       <c r="E11" s="9" t="str">
-        <v>Ingresos Financieros por Intereses de Financiamiento</v>
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Tributario)</v>
       </c>
       <c r="F11" s="10">
         <v>0</v>
       </c>
       <c r="G11" s="10">
-        <v>13924047.66</v>
+        <v>696202.38</v>
       </c>
       <c r="H11" s="9" t="str">
-        <v>Ingreso Gravable para ISLR</v>
+        <v>Pasivo Fiscal retenido por ONI C.A.</v>
       </c>
     </row>
     <row r="12">
@@ -12427,102 +13159,180 @@
         <v/>
       </c>
       <c r="D12" s="24" t="str">
+        <v>4.2.1.01.01</v>
+      </c>
+      <c r="E12" s="13" t="str">
+        <v>Ingresos Financieros por Intereses de Financiamiento</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>13924047.66</v>
+      </c>
+      <c r="H12" s="13" t="str">
+        <v>Ingreso Gravable para ISLR (Art. 529 C.Com)</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B13" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C13" s="8" t="str">
+        <v/>
+      </c>
+      <c r="D13" s="23" t="str">
         <v>1.1.2.03.01</v>
       </c>
-      <c r="E12" s="13" t="str">
+      <c r="E13" s="9" t="str">
         <v>Cuentas por Cobrar Socios (Amortización Capital)</v>
       </c>
-      <c r="F12" s="14">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14">
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10">
         <v>172451952.34</v>
       </c>
-      <c r="H12" s="13" t="str">
+      <c r="H13" s="9" t="str">
         <v>Saldo Vivo Capital: Bs. 420.47M</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="31" t="str">
+    <row r="14">
+      <c r="A14" s="32" t="str">
+        <v>Enteramiento SENIAT</v>
+      </c>
+      <c r="B14" s="12" t="str">
+        <v>30/11/2026</v>
+      </c>
+      <c r="C14" s="24" t="str">
+        <v>COMP-SENIAT-0001</v>
+      </c>
+      <c r="D14" s="24" t="str">
+        <v>2.1.3.01.03</v>
+      </c>
+      <c r="E14" s="13" t="str">
+        <v>Retenciones de ISLR por Enterar al SENIAT (Pasivo Extinguido)</v>
+      </c>
+      <c r="F14" s="14">
+        <v>696202.38</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="str">
+        <v>Planilla Oficial SENIAT / Art. 9 Dto. 1808</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B15" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C15" s="8" t="str">
+        <v/>
+      </c>
+      <c r="D15" s="23" t="str">
+        <v>1.1.1.02.01</v>
+      </c>
+      <c r="E15" s="9" t="str">
+        <v>Banco Banesco C.A. (Cuenta Corriente N° 5128) [Pago al SENIAT]</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10">
+        <v>696202.38</v>
+      </c>
+      <c r="H15" s="9" t="str">
+        <v>Transferencia electrónica Banesco a SENIAT</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="str">
         <v>Cierre Fiscal ISLR</v>
       </c>
-      <c r="B13" s="8" t="str">
+      <c r="B16" s="12" t="str">
         <v>31/12/2026</v>
       </c>
-      <c r="C13" s="23" t="str">
+      <c r="C16" s="24" t="str">
         <v>COMP-ISLR-0001</v>
       </c>
-      <c r="D13" s="23" t="str">
+      <c r="D16" s="24" t="str">
         <v>2.1.3.01.01</v>
       </c>
-      <c r="E13" s="9" t="str">
-        <v>Impuesto Sobre la Renta (ISLR) por Pagar</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="E16" s="13" t="str">
+        <v>Impuesto Sobre la Renta (ISLR) por Pagar (Pasivo DPJ-26)</v>
+      </c>
+      <c r="F16" s="14">
         <v>696202.38</v>
       </c>
-      <c r="G13" s="10">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="str">
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="str">
         <v>Compensación Fiscal contra Cuota Anual</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="str">
-        <v/>
-      </c>
-      <c r="B14" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C14" s="12" t="str">
-        <v/>
-      </c>
-      <c r="D14" s="24" t="str">
+    <row r="17">
+      <c r="A17" s="9" t="str">
+        <v/>
+      </c>
+      <c r="B17" s="8" t="str">
+        <v/>
+      </c>
+      <c r="C17" s="8" t="str">
+        <v/>
+      </c>
+      <c r="D17" s="23" t="str">
         <v>1.1.3.05.02</v>
       </c>
-      <c r="E14" s="13" t="str">
-        <v>Anticipo de ISLR Retenido por Clientes (5%)</v>
-      </c>
-      <c r="F14" s="14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
+      <c r="E17" s="9" t="str">
+        <v>Anticipo de ISLR por Compensar (5% Decreto 1808)</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0</v>
+      </c>
+      <c r="G17" s="10">
         <v>696202.38</v>
       </c>
-      <c r="H14" s="13" t="str">
-        <v>Descargo de Crédito Fiscal con ARC</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="str">
+      <c r="H17" s="9" t="str">
+        <v>Descargo formal de Anticipos en DPJ-26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="str">
         <v>TOTAL MAYOR CONSOLIDADO (SUMAS IGUALES):</v>
       </c>
-      <c r="B15" s="28" t="str">
-        <v/>
-      </c>
-      <c r="C15" s="28" t="str">
-        <v/>
-      </c>
-      <c r="D15" s="28" t="str">
-        <v/>
-      </c>
-      <c r="E15" s="17" t="str">
+      <c r="B18" s="28" t="str">
+        <v/>
+      </c>
+      <c r="C18" s="28" t="str">
+        <v/>
+      </c>
+      <c r="D18" s="28" t="str">
+        <v/>
+      </c>
+      <c r="E18" s="17" t="str">
         <v>Balance General Cuadrado</v>
       </c>
-      <c r="F15" s="18">
-        <v>1285472807.6800003</v>
-      </c>
-      <c r="G15" s="18">
-        <v>1285472807.68</v>
-      </c>
-      <c r="H15" s="17" t="str">
+      <c r="F18" s="18">
+        <v>1286865212.44</v>
+      </c>
+      <c r="G18" s="18">
+        <v>1286865212.44</v>
+      </c>
+      <c r="H18" s="17" t="str">
         <v>CUADRADO (SUMAS IGUALES)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12553,16 +13363,16 @@
       <c r="A4" s="6" t="str">
         <v>N°</v>
       </c>
-      <c r="B4" s="32" t="str">
+      <c r="B4" s="33" t="str">
         <v>Regla Contable Obligatoria</v>
       </c>
-      <c r="C4" s="32" t="str">
+      <c r="C4" s="33" t="str">
         <v>Base Jurídica Aplicable</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="33" t="str">
         <v>Principio Técnico / VEN-NIF</v>
       </c>
-      <c r="E4" s="32" t="str">
+      <c r="E4" s="33" t="str">
         <v>Descripción y Aplicación Obligatoria en la App</v>
       </c>
     </row>
@@ -12587,17 +13397,17 @@
       <c r="A6" s="24" t="str">
         <v>2</v>
       </c>
-      <c r="B6" s="33" t="str">
-        <v>Partida Cuádruple en Cobranzas con Intereses y Retención del 5% de ISLR</v>
+      <c r="B6" s="32" t="str">
+        <v>Partida Quíntuple en Cobranzas con Intereses y Retención del 5% de ISLR por Agrícola ONI C.A.</v>
       </c>
       <c r="C6" s="13" t="str">
-        <v>Art. 529 Código de Comercio y Art. 72 de la Ley de ISLR.</v>
+        <v>Art. 529 Código de Comercio, Art. 72 Ley de ISLR y Art. 9 Decreto N° 1.808.</v>
       </c>
       <c r="D6" s="13" t="str">
-        <v>Devengo Contable e Imputación Legal Imperativa de Pagos.</v>
+        <v>Devengo Contable, Cobranza Íntegra en Banco e Imputación Legal Imperativa de Pagos.</v>
       </c>
       <c r="E6" s="13" t="str">
-        <v>Cada uno de los 18 pagos recibidos debe descomponerse en 4 renglones obligatorios: 1) Entrada Líquida a Banco Banesco por el neto transferido, 2) Anticipo de ISLR 5% como Crédito Fiscal a favor de la empresa (Cuenta 1.1.3.05.02), 3) Reconocimiento de Ingresos Financieros por Intereses de Financiamiento (Cuenta 4.2.1.01.01), y 4) Disminución efectiva de la Cuenta por Cobrar al Socio (Amortización de Capital). Omitir el desglose de intereses o registrar todo a amortización de capital es causal de reparo tributario según el Art. 72 LISLR. [Aplicación en el sistema: Cada uno de los 18 recibos de pago genera su propio comprobante contable cuadruplicado, garantizando que sumas iguales cuadren exactamente al céntimo.]</v>
+        <v>Cada uno de los 18 pagos recibidos debe descomponerse en 5 renglones obligatorios: 1) Entrada Líquida a Banco Banesco por el monto íntegro transferido por el socio (Manuel Becerra es Persona Natural y no es agente de retención), 2) Anticipo de ISLR 5% como Crédito Fiscal a favor de la empresa (Cuenta 1.1.3.05.02), 3) Retenciones de ISLR por Enterar al SENIAT como Pasivo Tributario asumido por Agrícola ONI C.A. (Cuenta 2.1.3.01.03), 4) Reconocimiento de Ingresos Financieros por Intereses de Financiamiento (Cuenta 4.2.1.01.01), y 5) Disminución efectiva de la Cuenta por Cobrar al Socio (Amortización de Capital). Omitir el desglose de intereses o registrar todo a amortización de capital es causal de reparo tributario según el Art. 72 LISLR. [Aplicación en el sistema: Cada uno de los 18 recibos de pago genera su propio comprobante contable quíntuple, garantizando que sumas iguales cuadren exactamente al céntimo y reflejando que Agrícola ONI C.A. retiene y entera el impuesto al SENIAT.]</v>
       </c>
     </row>
     <row r="7">
@@ -12605,23 +13415,23 @@
         <v>3</v>
       </c>
       <c r="B7" s="31" t="str">
-        <v>Registro del Anticipo de ISLR Retenido como Activo Exigible (Crédito Fiscal)</v>
+        <v>Retención de ISLR asumida y enterada al SENIAT por Agrícola ONI C.A. (Crédito Fiscal)</v>
       </c>
       <c r="C7" s="9" t="str">
-        <v>Decreto N° 1.808 (Reglamento Parcial de Retenciones de la Ley de ISLR), Art. 9, Numeral 8.</v>
+        <v>Decreto N° 1.808 (Reglamento Parcial de Retenciones de la Ley de ISLR), Art. 9, Numeral 8 y Art. 27 del COT.</v>
       </c>
       <c r="D7" s="9" t="str">
-        <v>Tratamiento de Anticipos Impositivos conforme a VEN-NIF PYME Sección 29.</v>
+        <v>Tratamiento de Anticipos Impositivos y Retenciones en Fuente conforme a VEN-NIF PYME Sección 29.</v>
       </c>
       <c r="E7" s="9" t="str">
-        <v>El mutuario persona natural o jurídica debe practicar la retención del 5% sobre los intereses devengados al momento del pago y enterarla al Fisco Nacional emitiendo el comprobante ARC correspondiente. Para la empresa acreedora, dicho monto constituye un activo corriente exigible que se deduce directamente de la cuota tributaria a pagar en la Declaración Definitiva de Rentas del ejercicio. [Aplicación en el sistema: El sistema acumula el crédito fiscal retenido y genera el Asiento N° 48 de Cierre y Compensación Fiscal de ISLR deduciéndolo contra el pasivo tributario.]</v>
+        <v>Dado que el deudor es una persona natural no calificada como agente de retención ante el portal fiscal del SENIAT, la sociedad mercantil Agrícola ONI C.A. (como persona jurídica y sujeto corporativo) practica formalmente la retención del 5% de ISLR sobre los intereses de mutuo devengados, declarándola y enterándola directamente ante el SENIAT mediante su portal fiscal, registrando el pasivo por enterar y acreditando el anticipo tributario recuperable (Cuenta 1.1.3.05.02) que se deduce íntegramente de la cuota anual del ISLR corporativo. [Aplicación en el sistema: El sistema registra el pasivo y acumula el crédito fiscal retenido, generando los comprobantes de retención, de enteramiento al SENIAT y el Asiento de Cierre y Compensación Fiscal de ISLR.]</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="24" t="str">
         <v>4</v>
       </c>
-      <c r="B8" s="33" t="str">
+      <c r="B8" s="32" t="str">
         <v>Prelación Imperativa Mercantil: Intereses antes de Capital</v>
       </c>
       <c r="C8" s="13" t="str">
@@ -12682,7 +13492,7 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="str">
-        <v>LÍNEA DE CRÉDITO BS. 600.000.000,00 • MUTUARIO: Elías Rafael Trías Abreu (C.I. V-2.997.829)</v>
+        <v>LÍNEA DE CRÉDITO BS. 600.000.000,00 • MUTUARIO: Manuel Alejandro Becerra Luis (C.I. V-24.224.176)</v>
       </c>
     </row>
     <row r="3" ht="12" customHeight="1"/>
@@ -12735,7 +13545,7 @@
         <v>TRFMB-0134-3603818256</v>
       </c>
       <c r="E5" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F5" s="10">
         <v>2000000</v>
@@ -12770,7 +13580,7 @@
         <v>TRFMB-0134-3605046069</v>
       </c>
       <c r="E6" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F6" s="14">
         <v>365000</v>
@@ -12805,7 +13615,7 @@
         <v>TRFMB-0134-3605612140</v>
       </c>
       <c r="E7" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F7" s="10">
         <v>835000</v>
@@ -12840,7 +13650,7 @@
         <v>TRFMB-0134-3605630117</v>
       </c>
       <c r="E8" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F8" s="14">
         <v>4050000</v>
@@ -12875,7 +13685,7 @@
         <v>TRFMB-0134-3605630738</v>
       </c>
       <c r="E9" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F9" s="10">
         <v>36000000</v>
@@ -12910,7 +13720,7 @@
         <v>TRFMB-0134-3607248177</v>
       </c>
       <c r="E10" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F10" s="14">
         <v>500000</v>
@@ -12945,7 +13755,7 @@
         <v>TRFMB-0134-3607360183</v>
       </c>
       <c r="E11" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F11" s="10">
         <v>32500000</v>
@@ -12980,7 +13790,7 @@
         <v>TRFMB-0134-3607869982</v>
       </c>
       <c r="E12" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F12" s="14">
         <v>15000000</v>
@@ -13015,7 +13825,7 @@
         <v>TRFMB-0134-3607948391</v>
       </c>
       <c r="E13" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F13" s="10">
         <v>5000000</v>
@@ -13050,7 +13860,7 @@
         <v>TRFMB-0134-3607948940</v>
       </c>
       <c r="E14" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F14" s="14">
         <v>5000000.01</v>
@@ -13085,7 +13895,7 @@
         <v>TRFMB-0134-3607992268</v>
       </c>
       <c r="E15" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F15" s="10">
         <v>15000000</v>
@@ -13120,7 +13930,7 @@
         <v>TRFMB-0134-3608125055</v>
       </c>
       <c r="E16" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F16" s="14">
         <v>10000000</v>
@@ -13155,7 +13965,7 @@
         <v>TRFMB-0134-3608125960</v>
       </c>
       <c r="E17" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F17" s="10">
         <v>79790000</v>
@@ -13190,7 +14000,7 @@
         <v>TRFMB-0134-3608033529</v>
       </c>
       <c r="E18" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F18" s="14">
         <v>5000000</v>
@@ -13225,7 +14035,7 @@
         <v>TRFMB-0134-3609678714</v>
       </c>
       <c r="E19" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F19" s="10">
         <v>1000000</v>
@@ -13260,7 +14070,7 @@
         <v>TRFMB-0134-3610642810</v>
       </c>
       <c r="E20" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F20" s="14">
         <v>565000</v>
@@ -13295,7 +14105,7 @@
         <v>TRFMB-0134-3610770085</v>
       </c>
       <c r="E21" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F21" s="10">
         <v>26500000</v>
@@ -13330,7 +14140,7 @@
         <v>TRFMB-0134-3610925654</v>
       </c>
       <c r="E22" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F22" s="14">
         <v>150000</v>
@@ -13365,7 +14175,7 @@
         <v>TRFMB-0134-3611167966</v>
       </c>
       <c r="E23" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F23" s="10">
         <v>87900000</v>
@@ -13400,7 +14210,7 @@
         <v>TRFMB-0134-3611271343</v>
       </c>
       <c r="E24" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F24" s="14">
         <v>13120000</v>
@@ -13435,7 +14245,7 @@
         <v>TRFMB-0134-3611311850</v>
       </c>
       <c r="E25" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F25" s="10">
         <v>6875605.29</v>
@@ -13470,7 +14280,7 @@
         <v>TRFMB-0134-3611731383</v>
       </c>
       <c r="E26" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F26" s="14">
         <v>102000</v>
@@ -13505,7 +14315,7 @@
         <v>TRFMB-0134-3611731722</v>
       </c>
       <c r="E27" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F27" s="10">
         <v>101898000</v>
@@ -13540,7 +14350,7 @@
         <v>TRFMB-0134-61991611407</v>
       </c>
       <c r="E28" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F28" s="14">
         <v>200000</v>
@@ -13575,7 +14385,7 @@
         <v>TRFMB-0134-62021307849</v>
       </c>
       <c r="E29" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F29" s="10">
         <v>26400000</v>
@@ -13610,7 +14420,7 @@
         <v>TRFMB-0134-3615056914</v>
       </c>
       <c r="E30" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F30" s="14">
         <v>825000</v>
@@ -13645,7 +14455,7 @@
         <v>TRFMB-0134-3615099189</v>
       </c>
       <c r="E31" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F31" s="10">
         <v>825000</v>
@@ -13680,7 +14490,7 @@
         <v>TRFMB-0134-3616711990</v>
       </c>
       <c r="E32" s="13" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F32" s="14">
         <v>1000000</v>
@@ -13715,7 +14525,7 @@
         <v>TRFMB-0134-3619429622</v>
       </c>
       <c r="E33" s="9" t="str">
-        <v>Elías Rafael Trías Abreu</v>
+        <v>Manuel Alejandro Becerra Luis</v>
       </c>
       <c r="F33" s="10">
         <v>20000000</v>
@@ -13801,7 +14611,7 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="str">
-        <v>LÍNEA DE CRÉDITO BS. 600.000.000,00 • MUTUARIO PAGADOR: Elías Rafael Trías Abreu</v>
+        <v>LÍNEA DE CRÉDITO BS. 600.000.000,00 • MUTUARIO PAGADOR: Manuel Alejandro Becerra Luis</v>
       </c>
     </row>
     <row r="3" ht="12" customHeight="1"/>
